--- a/outputs/SA_historical_prices.xlsx
+++ b/outputs/SA_historical_prices.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Monthly Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Heatmap" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/SA_historical_prices.xlsx
+++ b/outputs/SA_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>91.23</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>111.42</v>
+        <v>109.49</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>92.29000000000001</v>
+        <v>89.28</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>112.83</v>
+        <v>110.72</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>97.06999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>113.03</v>
+        <v>112.07</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>99.59</v>
+        <v>97.84</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>115.97</v>
+        <v>114.85</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>89.91</v>
+        <v>89.08</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>104.84</v>
+        <v>104.22</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>93.42</v>
+        <v>92.38</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>108.96</v>
+        <v>108.14</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>96.73</v>
+        <v>96.77</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>112.43</v>
+        <v>112.38</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>105.33</v>
+        <v>105.18</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>122.53</v>
+        <v>122.24</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>90.98</v>
+        <v>91.03</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>109.74</v>
+        <v>109.7</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>107.32</v>
+        <v>107.23</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>129.98</v>
+        <v>129.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Mar 2026</t>
+          <t>Data through: Apr 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F274"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6233,6 +6233,26 @@
       </c>
       <c r="F274" s="7" t="inlineStr"/>
     </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>58.97</v>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>58.97</v>
+      </c>
+      <c r="F275" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6244,7 +6264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E274"/>
+  <dimension ref="A1:E275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11468,8 +11488,27 @@
         <v>35.84</v>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Apr 2026</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>58.97</v>
+      </c>
+      <c r="D275" s="5" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="E275" s="5" t="n">
+        <v>58.97</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B274">
+  <conditionalFormatting sqref="B2:B275">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11481,7 +11520,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C274">
+  <conditionalFormatting sqref="C2:C275">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11493,7 +11532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D274">
+  <conditionalFormatting sqref="D2:D275">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11505,7 +11544,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E274">
+  <conditionalFormatting sqref="E2:E275">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/SA_historical_prices.xlsx
+++ b/outputs/SA_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>88.40000000000001</v>
+        <v>86.11</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>109.49</v>
+        <v>106.66</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>89.28</v>
+        <v>87.75</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>110.72</v>
+        <v>108.91</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>95.5</v>
+        <v>92.17</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>112.07</v>
+        <v>108.57</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>97.84</v>
+        <v>95.42</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>114.85</v>
+        <v>112.47</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
+        <v>85.12</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>89.08</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>104.22</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>92.38</v>
-      </c>
       <c r="E7" s="5" t="n">
-        <v>108.14</v>
+        <v>103.98</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>96.77</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>112.38</v>
+        <v>111.51</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>105.18</v>
+        <v>106.01</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>122.24</v>
+        <v>122.58</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>91.03</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>109.7</v>
+        <v>109.35</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>107.23</v>
+        <v>108.35</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>129.76</v>
+        <v>130.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Apr 2026</t>
+          <t>Data through: May 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F275"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -690,10 +690,10 @@
         <v>34.07</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>49.64</v>
+        <v>50.33</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>62.46</v>
+        <v>63.32</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>26.44</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41.72</v>
+        <v>42.29</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>48.38</v>
+        <v>49.04</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>27.77</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>42.46</v>
+        <v>43.05</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>50.72</v>
+        <v>51.41</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>29.25</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>45.81</v>
+        <v>46.45</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>53.33</v>
+        <v>54.06</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>50.3</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>59.17</v>
+        <v>59.98</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>91.54000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>43.98</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>55.88</v>
+        <v>56.65</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>37.22</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>59.3</v>
+        <v>60.12</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>67.42</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>108.46</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>156.82</v>
+        <v>158.98</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>195.88</v>
+        <v>198.58</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>64.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>75.18000000000001</v>
+        <v>76.22</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>115.91</v>
+        <v>117.51</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>37.5</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>56.71</v>
+        <v>57.49</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.42</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>40.38</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>61.18</v>
+        <v>62.02</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>72.48999999999999</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>36.85</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>58.38</v>
+        <v>59.18</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>66.05</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>50.28</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>70.67</v>
+        <v>71.64</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>90</v>
+        <v>91.23999999999999</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>33.56</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>57.86</v>
+        <v>58.66</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>59.99</v>
+        <v>60.81</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>34.17</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>54.84</v>
+        <v>55.59</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>61</v>
+        <v>61.83</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>54.24</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>73.45</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>96.56999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>94.34999999999999</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>115.24</v>
+        <v>116.83</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>167.57</v>
+        <v>169.87</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>40.24</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>59.82</v>
+        <v>60.65</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>71.29000000000001</v>
+        <v>72.27</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>41.25</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>54.39</v>
+        <v>55.14</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>72.91</v>
+        <v>73.91</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>32.11</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>45.85</v>
+        <v>46.48</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>56.63</v>
+        <v>57.41</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>43.91</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>56.08</v>
+        <v>56.85</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>77.27</v>
+        <v>78.33</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>42.74</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>62.05</v>
+        <v>62.9</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>75.06</v>
+        <v>76.09</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>46.01</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>66.43000000000001</v>
+        <v>67.34</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>80.64</v>
+        <v>81.75</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>32.96</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>48.89</v>
+        <v>49.56</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>57.66</v>
+        <v>58.45</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>37.36</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>53.68</v>
+        <v>54.42</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>65.14</v>
+        <v>66.03</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>43.61</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>57.66</v>
+        <v>58.45</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>75.78</v>
+        <v>76.83</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>38.81</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>54.28</v>
+        <v>55.03</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>67.22</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>37.79</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>52.13</v>
+        <v>52.85</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>65.34</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>64.09</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>70.11</v>
+        <v>71.08</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>110.62</v>
+        <v>112.15</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>71.84999999999999</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>80.28</v>
+        <v>81.38</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>123.81</v>
+        <v>125.51</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>109.21</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>124.93</v>
+        <v>126.65</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>187.64</v>
+        <v>190.23</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>48.02</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>53.93</v>
+        <v>54.68</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>82.27</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>36.24</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>50.57</v>
+        <v>51.27</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>61.91</v>
+        <v>62.77</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>33.95</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>47.4</v>
+        <v>48.05</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>57.7</v>
+        <v>58.49</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>52.72</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>65.19</v>
+        <v>66.09</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>89.13</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>47.94</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>65.95999999999999</v>
+        <v>66.87</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>80.63</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>70.05</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>83.59</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>117.46</v>
+        <v>119.08</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>42.93</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>62.95</v>
+        <v>63.81</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>71.77</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>38.55</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>52.73</v>
+        <v>53.45</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>64.26000000000001</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>36.13</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>48.71</v>
+        <v>49.38</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>60.25</v>
+        <v>61.08</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>44.26</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>60.64</v>
+        <v>61.48</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>73.84</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>57.46</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>64.56999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>95.90000000000001</v>
+        <v>97.22</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>111.81</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>110.94</v>
+        <v>112.46</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>186.55</v>
+        <v>189.12</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>75.23999999999999</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>88.02</v>
+        <v>89.23</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>125.5</v>
+        <v>127.23</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>69.39</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>80.98999999999999</v>
+        <v>82.11</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>115.71</v>
+        <v>117.3</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>82.88</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>115.9</v>
+        <v>117.5</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>137.64</v>
+        <v>139.54</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>70.90000000000001</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>94.18000000000001</v>
+        <v>95.47</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>117.27</v>
+        <v>118.88</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>133.72</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>169.06</v>
+        <v>171.39</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>220.28</v>
+        <v>223.31</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>113.89</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>140.67</v>
+        <v>142.6</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>187.18</v>
+        <v>189.75</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>50.5</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>68.20999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>82.81</v>
+        <v>83.95</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>53.16</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>70.58</v>
+        <v>71.55</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>86.97</v>
+        <v>88.17</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>43.35</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>57.33</v>
+        <v>58.12</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>70.7</v>
+        <v>71.67</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>54.39</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>68.34999999999999</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>88.43000000000001</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>63.76</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>74.11</v>
+        <v>75.13</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>103.35</v>
+        <v>104.77</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>226.68</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>194.36</v>
+        <v>197.03</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>365.8</v>
+        <v>370.83</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>248.69</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>203.39</v>
+        <v>206.19</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>399.54</v>
+        <v>405.04</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>450.11</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>332.95</v>
+        <v>337.53</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>719.95</v>
+        <v>729.85</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>51.23</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>66.51000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>81.55</v>
+        <v>82.67</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>60.14</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>80.79000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>95.27</v>
+        <v>96.58</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>48.05</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>63.24</v>
+        <v>64.11</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>75.76000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>60.06</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>68.29000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>94.33</v>
+        <v>95.62</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>50.93</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>64.54000000000001</v>
+        <v>65.42</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>79.68000000000001</v>
+        <v>80.78</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>40.83</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>49.14</v>
+        <v>49.82</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>63.63</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>45.57</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>55.5</v>
+        <v>56.26</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>71.09999999999999</v>
+        <v>72.08</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>43.01</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>50.04</v>
+        <v>50.73</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>67.18000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>29.77</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>38.35</v>
+        <v>38.88</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>46.55</v>
+        <v>47.19</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>475</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>357.39</v>
+        <v>362.3</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>742.4400000000001</v>
+        <v>752.65</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>51.77</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>60.37</v>
+        <v>61.2</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>80.89</v>
+        <v>82</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>45.09</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>49.64</v>
+        <v>50.32</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>70.43000000000001</v>
+        <v>71.39</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>45.7</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>55.46</v>
+        <v>56.23</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>71.26000000000001</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>39.59</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>52.63</v>
+        <v>53.36</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>61.63</v>
+        <v>62.48</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>38.18</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>48.63</v>
+        <v>49.3</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>59.34</v>
+        <v>60.15</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>33.22</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.39</v>
+        <v>42.97</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.47</v>
+        <v>52.17</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>29.21</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.15</v>
+        <v>35.63</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>45.11</v>
+        <v>45.73</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>33.51</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>40.4</v>
+        <v>40.95</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>51.59</v>
+        <v>52.3</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>35.31</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>43</v>
+        <v>43.59</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>54.27</v>
+        <v>55.01</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>418.99</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>302.54</v>
+        <v>306.7</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>642.77</v>
+        <v>651.62</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>29.75</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36.49</v>
+        <v>36.99</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.56</v>
+        <v>46.18</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>190.57</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>148.65</v>
+        <v>150.69</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>290.93</v>
+        <v>294.93</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>267.21</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>200.95</v>
+        <v>203.72</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>406.67</v>
+        <v>412.27</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>27.63</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>35.78</v>
+        <v>36.27</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.92</v>
+        <v>42.5</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>36.87</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>44.76</v>
+        <v>45.38</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>55.83</v>
+        <v>56.6</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>34.27</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>45.3</v>
+        <v>45.93</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>51.79</v>
+        <v>52.5</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>40.33</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>53.43</v>
+        <v>54.17</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>60.82</v>
+        <v>61.66</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>32.6</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>44.05</v>
+        <v>44.66</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>49.05</v>
+        <v>49.72</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>31.21</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>38.98</v>
+        <v>39.51</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>46.84</v>
+        <v>47.49</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>31.03</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>37.55</v>
+        <v>38.07</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>46.46</v>
+        <v>47.1</v>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
     </row>
@@ -2430,10 +2430,10 @@
         <v>35.53</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>33.23</v>
+        <v>33.68</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>53.13</v>
+        <v>53.86</v>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
     </row>
@@ -2450,10 +2450,10 @@
         <v>30.93</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>33.71</v>
+        <v>34.17</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>46.19</v>
+        <v>46.83</v>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
     </row>
@@ -2470,10 +2470,10 @@
         <v>21.64</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>26.24</v>
+        <v>26.6</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>32.28</v>
+        <v>32.72</v>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
     </row>
@@ -2490,10 +2490,10 @@
         <v>208.38</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>153.02</v>
+        <v>155.12</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>309.21</v>
+        <v>313.46</v>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
     </row>
@@ -2510,10 +2510,10 @@
         <v>38.34</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>44.26</v>
+        <v>44.87</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>56.6</v>
+        <v>57.38</v>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
     </row>
@@ -2530,10 +2530,10 @@
         <v>27.5</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>32.86</v>
+        <v>33.31</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>40.39</v>
+        <v>40.95</v>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
     </row>
@@ -2550,10 +2550,10 @@
         <v>29.82</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>39.93</v>
+        <v>40.48</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>43.67</v>
+        <v>44.27</v>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
     </row>
@@ -2570,10 +2570,10 @@
         <v>38.76</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>49.04</v>
+        <v>49.71</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>56.58</v>
+        <v>57.36</v>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
     </row>
@@ -2590,10 +2590,10 @@
         <v>37.31</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>44.87</v>
+        <v>45.49</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>54.3</v>
+        <v>55.05</v>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
     </row>
@@ -2610,10 +2610,10 @@
         <v>42.39</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>48.11</v>
+        <v>48.77</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>61.57</v>
+        <v>62.42</v>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
     </row>
@@ -2630,10 +2630,10 @@
         <v>38.44</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>49.95</v>
+        <v>50.64</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>55.72</v>
+        <v>56.49</v>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
     </row>
@@ -2650,10 +2650,10 @@
         <v>44.12</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>54.93</v>
+        <v>55.69</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>63.83</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
     </row>
@@ -2670,10 +2670,10 @@
         <v>52.46</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>58.29</v>
+        <v>59.09</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>75.90000000000001</v>
+        <v>76.94</v>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
     </row>
@@ -2690,10 +2690,10 @@
         <v>35.82</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>44.39</v>
+        <v>45</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>51.82</v>
+        <v>52.54</v>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
     </row>
@@ -2710,10 +2710,10 @@
         <v>27.64</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>34.39</v>
+        <v>34.86</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>39.99</v>
+        <v>40.54</v>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
     </row>
@@ -2730,10 +2730,10 @@
         <v>31.12</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>37.06</v>
+        <v>37.57</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>45.02</v>
+        <v>45.63</v>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
     </row>
@@ -2750,10 +2750,10 @@
         <v>31.06</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>39.27</v>
+        <v>39.81</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>44.92</v>
+        <v>45.54</v>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
     </row>
@@ -2770,10 +2770,10 @@
         <v>29.6</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>37.22</v>
+        <v>37.73</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>42.8</v>
+        <v>43.39</v>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
     </row>
@@ -2790,10 +2790,10 @@
         <v>29.99</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>42.02</v>
+        <v>42.6</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>43.29</v>
+        <v>43.88</v>
       </c>
       <c r="F107" s="7" t="inlineStr"/>
     </row>
@@ -2810,10 +2810,10 @@
         <v>32.16</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>41.93</v>
+        <v>42.51</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>46.34</v>
+        <v>46.98</v>
       </c>
       <c r="F108" s="7" t="inlineStr"/>
     </row>
@@ -2830,10 +2830,10 @@
         <v>42.59</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>37.67</v>
+        <v>38.19</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>61.27</v>
+        <v>62.11</v>
       </c>
       <c r="F109" s="7" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>97.23</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>114.17</v>
+        <v>115.74</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>139.23</v>
+        <v>141.15</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
         <v>65.08</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>90.27</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>92.77</v>
+        <v>94.05</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2898,10 +2898,10 @@
         <v>61.09</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>76.34999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>86.7</v>
+        <v>87.89</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
         <v>55.05</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>72.26000000000001</v>
+        <v>73.25</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>78.06</v>
+        <v>79.13</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         <v>78.5</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>92.43000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>111.21</v>
+        <v>112.74</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -2970,10 +2970,10 @@
         <v>60.95</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>75.59999999999999</v>
+        <v>76.64</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>86.28</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         <v>74.05</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>83.59</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>104.7</v>
+        <v>106.14</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
         <v>63.97</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>82.67</v>
+        <v>83.8</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>90.34999999999999</v>
+        <v>91.59</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -3042,10 +3042,10 @@
         <v>67.98</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>81.34999999999999</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>95.90000000000001</v>
+        <v>97.22</v>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         <v>92.58</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>108.34</v>
+        <v>109.83</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>130.44</v>
+        <v>132.24</v>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
         <v>137.04</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>153.03</v>
+        <v>155.14</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>192.84</v>
+        <v>195.5</v>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         <v>161.64</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>153.63</v>
+        <v>155.74</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>227.17</v>
+        <v>230.3</v>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
@@ -3138,10 +3138,10 @@
         <v>80.34999999999999</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>97.48999999999999</v>
+        <v>98.83</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>112.47</v>
+        <v>114.02</v>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
@@ -3162,10 +3162,10 @@
         <v>82.62</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>99.31999999999999</v>
+        <v>100.68</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>115.18</v>
+        <v>116.77</v>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         <v>73.02</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>85.12</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>101.39</v>
+        <v>102.78</v>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>64.76000000000001</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>79.58</v>
+        <v>80.67</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>89.7</v>
+        <v>90.94</v>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         <v>54.57</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>68.83</v>
+        <v>69.78</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>75.41</v>
+        <v>76.45</v>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         <v>119</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>109.69</v>
+        <v>111.2</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>164.05</v>
+        <v>166.31</v>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
         <v>137.47</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>122.27</v>
+        <v>123.96</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>189.14</v>
+        <v>191.74</v>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>59.75</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>78.93000000000001</v>
+        <v>80.02</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>82.05</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
         <v>55.71</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>67.39</v>
+        <v>68.31</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>76.34999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         <v>51.23</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>65.86</v>
+        <v>66.77</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>70.09</v>
+        <v>71.06</v>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         <v>58.5</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>71</v>
+        <v>71.98</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>79.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
         <v>59.79</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>74.20999999999999</v>
+        <v>75.23</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>81.53</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         <v>60.81</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>70.48</v>
+        <v>71.45</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>82.8</v>
+        <v>83.94</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>50.71</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>56.65</v>
+        <v>57.43</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>68.95</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>49.36</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>55.75</v>
+        <v>56.52</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>67.02</v>
+        <v>67.95</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>34.86</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>43.45</v>
+        <v>44.05</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>47.31</v>
+        <v>47.96</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>35.52</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>44.37</v>
+        <v>44.98</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>48.17</v>
+        <v>48.83</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>31.78</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>38.82</v>
+        <v>39.35</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>43.07</v>
+        <v>43.66</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>47.98</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>46.97</v>
+        <v>47.62</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>64.98999999999999</v>
+        <v>65.88</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>49.24</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>60.71</v>
+        <v>61.54</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>66.65000000000001</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>34.48</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>38.61</v>
+        <v>39.14</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>46.64</v>
+        <v>47.28</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>49.75</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>53.91</v>
+        <v>54.66</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>67.14</v>
+        <v>68.06</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>43.01</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>51.19</v>
+        <v>51.89</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>57.91</v>
+        <v>58.7</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>87.84</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>78.72</v>
+        <v>79.81</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>117.98</v>
+        <v>119.61</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>105.03</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>98.61</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>140.89</v>
+        <v>142.83</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>64.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>81.31999999999999</v>
+        <v>82.44</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>86.77</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>72.77</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>79.03</v>
+        <v>80.12</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>97.36</v>
+        <v>98.7</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>51.88</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>54.92</v>
+        <v>55.67</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>69.31999999999999</v>
+        <v>70.28</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>63.99</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>65.23</v>
+        <v>66.13</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>85.40000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>97.42</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>89.06999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>129.84</v>
+        <v>131.63</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>71.81</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>67.03</v>
+        <v>67.95</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>95.77</v>
+        <v>97.09</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>53.34</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>54.34</v>
+        <v>55.09</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>71.19</v>
+        <v>72.17</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>73.59</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>73.89</v>
+        <v>74.91</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>98.28</v>
+        <v>99.63</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>63.34</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>84.45999999999999</v>
+        <v>85.63</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>101.4</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>94.14</v>
+        <v>95.44</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>135.02</v>
+        <v>136.88</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>162.44</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>163.68</v>
+        <v>165.93</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>215.98</v>
+        <v>218.95</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>376.22</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>304.29</v>
+        <v>308.48</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>499.06</v>
+        <v>505.93</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>86.52</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>87.66</v>
+        <v>88.87</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>114.5</v>
+        <v>116.08</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>70.70999999999999</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>79.02</v>
+        <v>80.11</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>93.36</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>71.86</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>78.11</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>94.70999999999999</v>
+        <v>96.02</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>81.73999999999999</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>81.43000000000001</v>
+        <v>82.55</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>107.55</v>
+        <v>109.03</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>92.59</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>127.8</v>
+        <v>129.55</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>121.61</v>
+        <v>123.28</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>102.67</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>110.5</v>
+        <v>112.02</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>134.64</v>
+        <v>136.5</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>298.82</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>235.5</v>
+        <v>238.74</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>391.28</v>
+        <v>396.67</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>164.54</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>160.03</v>
+        <v>162.23</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>215.13</v>
+        <v>218.09</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>140.44</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>156.39</v>
+        <v>158.54</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>183.5</v>
+        <v>186.02</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>134.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>155.58</v>
+        <v>157.72</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>175.73</v>
+        <v>178.14</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>113.03</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>142.01</v>
+        <v>143.96</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>147.49</v>
+        <v>149.52</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>127.48</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>147.78</v>
+        <v>149.81</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>166.01</v>
+        <v>168.29</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>126.76</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>136.95</v>
+        <v>138.84</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>164.74</v>
+        <v>167</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>80.16</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>95.44</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>103.96</v>
+        <v>105.39</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>76.89</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>89.76000000000001</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>99.5</v>
+        <v>100.87</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>110.15</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>117.14</v>
+        <v>118.75</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>142.22</v>
+        <v>144.18</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>93.62</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>107.59</v>
+        <v>109.07</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>120.61</v>
+        <v>122.27</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>231.26</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>204.23</v>
+        <v>207.04</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>297.5</v>
+        <v>301.59</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>143.22</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>140.24</v>
+        <v>142.16</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>183.97</v>
+        <v>186.51</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>89.47</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>103.51</v>
+        <v>104.94</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>114.76</v>
+        <v>116.34</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>134.3</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>126.03</v>
+        <v>127.76</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>172.06</v>
+        <v>174.43</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>105.82</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>113.26</v>
+        <v>114.82</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>135.41</v>
+        <v>137.27</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>125.64</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>135.38</v>
+        <v>137.24</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>160.58</v>
+        <v>162.79</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>147.26</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>134.99</v>
+        <v>136.85</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>187.95</v>
+        <v>190.53</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>89.47</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>92.16</v>
+        <v>93.42</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>114.02</v>
+        <v>115.59</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>102.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>115.3</v>
+        <v>116.88</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>130.51</v>
+        <v>132.3</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>105.22</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>124.65</v>
+        <v>126.37</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>133.67</v>
+        <v>135.51</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>102.27</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>125.26</v>
+        <v>126.98</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>129.7</v>
+        <v>131.48</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>111.5</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>116.96</v>
+        <v>118.56</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>141.16</v>
+        <v>143.1</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>407.47</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>305.15</v>
+        <v>309.35</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>515.89</v>
+        <v>522.99</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>117.28</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>140.2</v>
+        <v>142.13</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>148.49</v>
+        <v>150.53</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>175.2</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>166.63</v>
+        <v>168.92</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>221.84</v>
+        <v>224.89</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>97.14</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>118.58</v>
+        <v>120.22</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>122.75</v>
+        <v>124.44</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>92.58</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>107.03</v>
+        <v>108.5</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>116.76</v>
+        <v>118.37</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>113.86</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>120.46</v>
+        <v>122.12</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>143.32</v>
+        <v>145.29</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>92.31999999999999</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>92.88</v>
+        <v>94.16</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>115.99</v>
+        <v>117.58</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>99.59</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>98.79000000000001</v>
+        <v>100.15</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>124.89</v>
+        <v>126.6</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>81.09999999999999</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>91.31</v>
+        <v>92.56</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>101.51</v>
+        <v>102.91</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>69.06999999999999</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>84.09</v>
+        <v>85.25</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>86.25</v>
+        <v>87.44</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>34.58</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>63.37</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>43.09</v>
+        <v>43.68</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>123.62</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>104.46</v>
+        <v>105.9</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>153.67</v>
+        <v>155.79</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>124.39</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>103.3</v>
+        <v>104.72</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>154.44</v>
+        <v>156.57</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>75.56</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>79.59</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>93.7</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>64.53</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>58.15</v>
+        <v>58.95</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>79.92</v>
+        <v>81.02</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>40.07</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>41.76</v>
+        <v>42.33</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>49.95</v>
+        <v>50.64</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>44.77</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>46.75</v>
+        <v>47.39</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>56.17</v>
+        <v>56.94</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>64.04000000000001</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>63.48</v>
+        <v>64.36</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>80.87</v>
+        <v>81.98</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>68.84999999999999</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>74.54000000000001</v>
+        <v>75.56</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>86.5</v>
+        <v>87.69</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>56.61</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>56.96</v>
+        <v>57.74</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>70.76000000000001</v>
+        <v>71.73</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>7.52</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>18.91</v>
+        <v>19.18</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>9.35</v>
+        <v>9.48</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>40.23</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>40.88</v>
+        <v>41.44</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>49.88</v>
+        <v>50.57</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>37.9</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>45.39</v>
+        <v>46.01</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>46.85</v>
+        <v>47.49</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>10.26</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>20.68</v>
+        <v>20.96</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>12.64</v>
+        <v>12.82</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>12.41</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>35.3</v>
+        <v>35.79</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>15.27</v>
+        <v>15.48</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>25.88</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>27.61</v>
+        <v>27.99</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>31.77</v>
+        <v>32.21</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>82.06999999999999</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>84.27</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>100.57</v>
+        <v>101.95</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>62.15</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>63.73</v>
+        <v>64.61</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>75.97</v>
+        <v>77.02</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>111.31</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>89</v>
+        <v>90.23</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>135.73</v>
+        <v>137.6</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>96.95999999999999</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>102.66</v>
+        <v>104.07</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>117.95</v>
+        <v>119.57</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>117.5</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>110.61</v>
+        <v>112.14</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>142.53</v>
+        <v>144.49</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>46.43</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>52.54</v>
+        <v>53.27</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>56.16</v>
+        <v>56.93</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>18.34</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>22.64</v>
+        <v>22.95</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>22.12</v>
+        <v>22.43</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>9.65</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>17.46</v>
+        <v>17.7</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>11.59</v>
+        <v>11.75</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>43.67</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>45.08</v>
+        <v>45.7</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>52.23</v>
+        <v>52.95</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>93.66</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>83.75</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>111.55</v>
+        <v>113.09</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>120.28</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>105.17</v>
+        <v>106.62</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>142.23</v>
+        <v>144.19</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>44.11</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>63.66</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>51.79</v>
+        <v>52.5</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>68.09</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>78.11</v>
+        <v>79.19</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>79.38</v>
+        <v>80.47</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>168.67</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>176.57</v>
+        <v>179</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>195.48</v>
+        <v>198.16</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>403.15</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>359.8</v>
+        <v>364.75</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>464.46</v>
+        <v>470.85</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>349.33</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>346.57</v>
+        <v>351.33</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>400.1</v>
+        <v>405.6</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>489.22</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>424.03</v>
+        <v>429.86</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>556.91</v>
+        <v>564.5700000000001</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>226.62</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>195.79</v>
+        <v>198.48</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>256.41</v>
+        <v>259.94</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>137.68</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>166.27</v>
+        <v>168.56</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>154.84</v>
+        <v>156.97</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>68.95</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>104.5</v>
+        <v>105.94</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>77.06999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>55.1</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>69.45</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>61.21</v>
+        <v>62.06</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>14.86</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>39.12</v>
+        <v>39.66</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>16.41</v>
+        <v>16.63</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>41.16</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>62.88</v>
+        <v>63.74</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>45.25</v>
+        <v>45.87</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>130.19</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>106.21</v>
+        <v>107.67</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>142.47</v>
+        <v>144.43</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>54.46</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>70.73</v>
+        <v>71.7</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>59.33</v>
+        <v>60.15</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>81.17</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>92.36</v>
+        <v>93.63</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>88.18000000000001</v>
+        <v>89.39</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>236.79</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>214.81</v>
+        <v>217.76</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>256.51</v>
+        <v>260.04</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>125.95</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>92.45999999999999</v>
+        <v>93.73</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>136.05</v>
+        <v>137.93</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>94.95999999999999</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>78.3</v>
+        <v>79.37</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>102.19</v>
+        <v>103.59</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>216.23</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>171.8</v>
+        <v>174.16</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>231.8</v>
+        <v>234.98</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>34.35</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>44.13</v>
+        <v>44.73</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>36.68</v>
+        <v>37.19</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>9.57</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>16.11</v>
+        <v>16.33</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>10.2</v>
+        <v>10.34</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>48.53</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>47.77</v>
+        <v>48.43</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>51.61</v>
+        <v>52.32</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>45.54</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>40.36</v>
+        <v>40.91</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>48.33</v>
+        <v>48.99</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>23.49</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>34.64</v>
+        <v>35.11</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>24.85</v>
+        <v>25.19</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>74.73999999999999</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>69.68000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>78.83</v>
+        <v>79.91</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>70.23999999999999</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>70.58</v>
+        <v>71.56</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>73.84999999999999</v>
+        <v>74.87</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>81.98999999999999</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>96.92</v>
+        <v>98.25</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>85.91</v>
+        <v>87.09</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5786,10 +5786,10 @@
         <v>143.45</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>141.7</v>
+        <v>143.65</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>149.79</v>
+        <v>151.85</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5806,10 +5806,10 @@
         <v>212.87</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>183.85</v>
+        <v>186.37</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>221.5</v>
+        <v>224.55</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5826,10 +5826,10 @@
         <v>295.38</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>250.82</v>
+        <v>254.27</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>307.14</v>
+        <v>311.36</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5846,10 +5846,10 @@
         <v>219.7</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>155.36</v>
+        <v>157.5</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>228.28</v>
+        <v>231.42</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
     </row>
@@ -5866,10 +5866,10 @@
         <v>144.76</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>83.36</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>150.3</v>
+        <v>152.37</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
     </row>
@@ -5886,10 +5886,10 @@
         <v>29.04</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>36.57</v>
+        <v>37.07</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>30.13</v>
+        <v>30.55</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
@@ -5906,10 +5906,10 @@
         <v>49.02</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>63.16</v>
+        <v>64.03</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>50.83</v>
+        <v>51.53</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
     </row>
@@ -5926,10 +5926,10 @@
         <v>47.42</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>63.7</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>49.14</v>
+        <v>49.82</v>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
     </row>
@@ -5946,10 +5946,10 @@
         <v>8.76</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>49.82</v>
+        <v>50.5</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>9.050000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
     </row>
@@ -5966,10 +5966,10 @@
         <v>87.75</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>94.08</v>
+        <v>95.37</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>90.38</v>
+        <v>91.62</v>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
     </row>
@@ -5986,10 +5986,10 @@
         <v>55.45</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>63.45</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>56.94</v>
+        <v>57.72</v>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>82.23</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>90.98</v>
+        <v>92.23</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>84.23</v>
+        <v>85.38</v>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
     </row>
@@ -6026,10 +6026,10 @@
         <v>93.44</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>85.12</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>95.47</v>
+        <v>96.78</v>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
     </row>
@@ -6046,10 +6046,10 @@
         <v>424.64</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>255.21</v>
+        <v>258.72</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>432.79</v>
+        <v>438.75</v>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
     </row>
@@ -6066,10 +6066,10 @@
         <v>223.67</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>167.38</v>
+        <v>169.68</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>226.97</v>
+        <v>230.09</v>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
     </row>
@@ -6086,10 +6086,10 @@
         <v>84.67</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>87.76000000000001</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>85.54000000000001</v>
+        <v>86.72</v>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
     </row>
@@ -6106,10 +6106,10 @@
         <v>57.7</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>57.94</v>
+        <v>58.74</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>58.04</v>
+        <v>58.84</v>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
     </row>
@@ -6126,10 +6126,10 @@
         <v>40.14</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>50.37</v>
+        <v>51.06</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>40.3</v>
+        <v>40.85</v>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
     </row>
@@ -6146,10 +6146,10 @@
         <v>9.94</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>32.54</v>
+        <v>32.99</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>9.960000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
     </row>
@@ -6166,10 +6166,10 @@
         <v>-0.41</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>27.92</v>
+        <v>28.3</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="F271" s="7" t="inlineStr"/>
     </row>
@@ -6186,10 +6186,10 @@
         <v>250.71</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>152.25</v>
+        <v>153.64</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>250.71</v>
+        <v>253</v>
       </c>
       <c r="F272" s="7" t="inlineStr"/>
     </row>
@@ -6206,10 +6206,10 @@
         <v>34.52</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>56</v>
+        <v>56.25</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>34.52</v>
+        <v>34.68</v>
       </c>
       <c r="F273" s="7" t="inlineStr"/>
     </row>
@@ -6252,6 +6252,26 @@
         <v>58.97</v>
       </c>
       <c r="F275" s="7" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="n">
+        <v>55.79</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v>55.79</v>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="F276" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6264,7 +6284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E275"/>
+  <dimension ref="A1:E276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6314,10 +6334,10 @@
         <v>34.07</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>49.64</v>
+        <v>50.33</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>62.46</v>
+        <v>63.32</v>
       </c>
     </row>
     <row r="3">
@@ -6333,10 +6353,10 @@
         <v>26.44</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>41.72</v>
+        <v>42.29</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>48.38</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="4">
@@ -6352,10 +6372,10 @@
         <v>27.77</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>42.46</v>
+        <v>43.05</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>50.72</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="5">
@@ -6371,10 +6391,10 @@
         <v>29.25</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>45.81</v>
+        <v>46.45</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>53.33</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="6">
@@ -6390,10 +6410,10 @@
         <v>50.3</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>59.17</v>
+        <v>59.98</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>91.54000000000001</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="7">
@@ -6409,10 +6429,10 @@
         <v>43.98</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>55.88</v>
+        <v>56.65</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
@@ -6428,10 +6448,10 @@
         <v>37.22</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>59.3</v>
+        <v>60.12</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>67.42</v>
+        <v>68.34999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -6447,10 +6467,10 @@
         <v>108.46</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>156.82</v>
+        <v>158.98</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>195.88</v>
+        <v>198.58</v>
       </c>
     </row>
     <row r="10">
@@ -6466,10 +6486,10 @@
         <v>64.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>75.18000000000001</v>
+        <v>76.22</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>115.91</v>
+        <v>117.51</v>
       </c>
     </row>
     <row r="11">
@@ -6485,10 +6505,10 @@
         <v>37.5</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>56.71</v>
+        <v>57.49</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>67.42</v>
+        <v>68.34999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -6504,10 +6524,10 @@
         <v>40.38</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>61.18</v>
+        <v>62.02</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>72.48999999999999</v>
+        <v>73.48999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -6523,10 +6543,10 @@
         <v>36.85</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>58.38</v>
+        <v>59.18</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>66.05</v>
+        <v>66.95999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6542,10 +6562,10 @@
         <v>50.28</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>70.67</v>
+        <v>71.64</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>90</v>
+        <v>91.23999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -6561,10 +6581,10 @@
         <v>33.56</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>57.86</v>
+        <v>58.66</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>59.99</v>
+        <v>60.81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,10 +6600,10 @@
         <v>34.17</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>54.84</v>
+        <v>55.59</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>61</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="17">
@@ -6599,10 +6619,10 @@
         <v>54.24</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>73.45</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>96.56999999999999</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -6618,10 +6638,10 @@
         <v>94.34999999999999</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>115.24</v>
+        <v>116.83</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>167.57</v>
+        <v>169.87</v>
       </c>
     </row>
     <row r="19">
@@ -6637,10 +6657,10 @@
         <v>40.24</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>59.82</v>
+        <v>60.65</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>71.29000000000001</v>
+        <v>72.27</v>
       </c>
     </row>
     <row r="20">
@@ -6656,10 +6676,10 @@
         <v>41.25</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>54.39</v>
+        <v>55.14</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>72.91</v>
+        <v>73.91</v>
       </c>
     </row>
     <row r="21">
@@ -6675,10 +6695,10 @@
         <v>32.11</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>45.85</v>
+        <v>46.48</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>56.63</v>
+        <v>57.41</v>
       </c>
     </row>
     <row r="22">
@@ -6694,10 +6714,10 @@
         <v>43.91</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>56.08</v>
+        <v>56.85</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>77.27</v>
+        <v>78.33</v>
       </c>
     </row>
     <row r="23">
@@ -6713,10 +6733,10 @@
         <v>42.74</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>62.05</v>
+        <v>62.9</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>75.06</v>
+        <v>76.09</v>
       </c>
     </row>
     <row r="24">
@@ -6732,10 +6752,10 @@
         <v>46.01</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>66.43000000000001</v>
+        <v>67.34</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>80.64</v>
+        <v>81.75</v>
       </c>
     </row>
     <row r="25">
@@ -6751,10 +6771,10 @@
         <v>32.96</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>48.89</v>
+        <v>49.56</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>57.66</v>
+        <v>58.45</v>
       </c>
     </row>
     <row r="26">
@@ -6770,10 +6790,10 @@
         <v>37.36</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>53.68</v>
+        <v>54.42</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>65.14</v>
+        <v>66.03</v>
       </c>
     </row>
     <row r="27">
@@ -6789,10 +6809,10 @@
         <v>43.61</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>57.66</v>
+        <v>58.45</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>75.78</v>
+        <v>76.83</v>
       </c>
     </row>
     <row r="28">
@@ -6808,10 +6828,10 @@
         <v>38.81</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>54.28</v>
+        <v>55.03</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>67.22</v>
+        <v>68.15000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -6827,10 +6847,10 @@
         <v>37.79</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>52.13</v>
+        <v>52.85</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>65.34</v>
+        <v>66.23999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -6846,10 +6866,10 @@
         <v>64.09</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>70.11</v>
+        <v>71.08</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>110.62</v>
+        <v>112.15</v>
       </c>
     </row>
     <row r="31">
@@ -6865,10 +6885,10 @@
         <v>71.84999999999999</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>80.28</v>
+        <v>81.38</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>123.81</v>
+        <v>125.51</v>
       </c>
     </row>
     <row r="32">
@@ -6884,10 +6904,10 @@
         <v>109.21</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>124.93</v>
+        <v>126.65</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>187.64</v>
+        <v>190.23</v>
       </c>
     </row>
     <row r="33">
@@ -6903,10 +6923,10 @@
         <v>48.02</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>53.93</v>
+        <v>54.68</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>82.27</v>
+        <v>83.40000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -6922,10 +6942,10 @@
         <v>36.24</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>50.57</v>
+        <v>51.27</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>61.91</v>
+        <v>62.77</v>
       </c>
     </row>
     <row r="35">
@@ -6941,10 +6961,10 @@
         <v>33.95</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>47.4</v>
+        <v>48.05</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>57.7</v>
+        <v>58.49</v>
       </c>
     </row>
     <row r="36">
@@ -6960,10 +6980,10 @@
         <v>52.72</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>65.19</v>
+        <v>66.09</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>89.13</v>
+        <v>90.34999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -6979,10 +6999,10 @@
         <v>47.94</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>65.95999999999999</v>
+        <v>66.87</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>80.63</v>
+        <v>81.73999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -6998,10 +7018,10 @@
         <v>70.05</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>83.59</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>117.46</v>
+        <v>119.08</v>
       </c>
     </row>
     <row r="39">
@@ -7017,10 +7037,10 @@
         <v>42.93</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>62.95</v>
+        <v>63.81</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>71.77</v>
+        <v>72.76000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -7036,10 +7056,10 @@
         <v>38.55</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>52.73</v>
+        <v>53.45</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>64.26000000000001</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -7055,10 +7075,10 @@
         <v>36.13</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>48.71</v>
+        <v>49.38</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>60.25</v>
+        <v>61.08</v>
       </c>
     </row>
     <row r="42">
@@ -7074,10 +7094,10 @@
         <v>44.26</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>60.64</v>
+        <v>61.48</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>73.84</v>
+        <v>74.84999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -7093,10 +7113,10 @@
         <v>57.46</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>64.56999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>95.90000000000001</v>
+        <v>97.22</v>
       </c>
     </row>
     <row r="44">
@@ -7112,10 +7132,10 @@
         <v>111.81</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>110.94</v>
+        <v>112.46</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>186.55</v>
+        <v>189.12</v>
       </c>
     </row>
     <row r="45">
@@ -7131,10 +7151,10 @@
         <v>75.23999999999999</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>88.02</v>
+        <v>89.23</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>125.5</v>
+        <v>127.23</v>
       </c>
     </row>
     <row r="46">
@@ -7150,10 +7170,10 @@
         <v>69.39</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>80.98999999999999</v>
+        <v>82.11</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>115.71</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="47">
@@ -7169,10 +7189,10 @@
         <v>82.88</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>115.9</v>
+        <v>117.5</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>137.64</v>
+        <v>139.54</v>
       </c>
     </row>
     <row r="48">
@@ -7188,10 +7208,10 @@
         <v>70.90000000000001</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>94.18000000000001</v>
+        <v>95.47</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>117.27</v>
+        <v>118.88</v>
       </c>
     </row>
     <row r="49">
@@ -7207,10 +7227,10 @@
         <v>133.72</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>169.06</v>
+        <v>171.39</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>220.28</v>
+        <v>223.31</v>
       </c>
     </row>
     <row r="50">
@@ -7226,10 +7246,10 @@
         <v>113.89</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>140.67</v>
+        <v>142.6</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>187.18</v>
+        <v>189.75</v>
       </c>
     </row>
     <row r="51">
@@ -7245,10 +7265,10 @@
         <v>50.5</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>68.20999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>82.81</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="52">
@@ -7264,10 +7284,10 @@
         <v>53.16</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>70.58</v>
+        <v>71.55</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>86.97</v>
+        <v>88.17</v>
       </c>
     </row>
     <row r="53">
@@ -7283,10 +7303,10 @@
         <v>43.35</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>57.33</v>
+        <v>58.12</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>70.7</v>
+        <v>71.67</v>
       </c>
     </row>
     <row r="54">
@@ -7302,10 +7322,10 @@
         <v>54.39</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>68.34999999999999</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>88.43000000000001</v>
+        <v>89.65000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -7321,10 +7341,10 @@
         <v>63.76</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>74.11</v>
+        <v>75.13</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>103.35</v>
+        <v>104.77</v>
       </c>
     </row>
     <row r="56">
@@ -7340,10 +7360,10 @@
         <v>226.68</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>194.36</v>
+        <v>197.03</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>365.8</v>
+        <v>370.83</v>
       </c>
     </row>
     <row r="57">
@@ -7359,10 +7379,10 @@
         <v>248.69</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>203.39</v>
+        <v>206.19</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>399.54</v>
+        <v>405.04</v>
       </c>
     </row>
     <row r="58">
@@ -7378,10 +7398,10 @@
         <v>450.11</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>332.95</v>
+        <v>337.53</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>719.95</v>
+        <v>729.85</v>
       </c>
     </row>
     <row r="59">
@@ -7397,10 +7417,10 @@
         <v>51.23</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>66.51000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>81.55</v>
+        <v>82.67</v>
       </c>
     </row>
     <row r="60">
@@ -7416,10 +7436,10 @@
         <v>60.14</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>80.79000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>95.27</v>
+        <v>96.58</v>
       </c>
     </row>
     <row r="61">
@@ -7435,10 +7455,10 @@
         <v>48.05</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>63.24</v>
+        <v>64.11</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>75.76000000000001</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="62">
@@ -7454,10 +7474,10 @@
         <v>60.06</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>68.29000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>94.33</v>
+        <v>95.62</v>
       </c>
     </row>
     <row r="63">
@@ -7473,10 +7493,10 @@
         <v>50.93</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>64.54000000000001</v>
+        <v>65.42</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>79.68000000000001</v>
+        <v>80.78</v>
       </c>
     </row>
     <row r="64">
@@ -7492,10 +7512,10 @@
         <v>40.83</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>49.14</v>
+        <v>49.82</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>63.63</v>
+        <v>64.51000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -7511,10 +7531,10 @@
         <v>45.57</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>55.5</v>
+        <v>56.26</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>71.09999999999999</v>
+        <v>72.08</v>
       </c>
     </row>
     <row r="66">
@@ -7530,10 +7550,10 @@
         <v>43.01</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>50.04</v>
+        <v>50.73</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>67.18000000000001</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -7549,10 +7569,10 @@
         <v>29.77</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>38.35</v>
+        <v>38.88</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>46.55</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="68">
@@ -7568,10 +7588,10 @@
         <v>475</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>357.39</v>
+        <v>362.3</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>742.4400000000001</v>
+        <v>752.65</v>
       </c>
     </row>
     <row r="69">
@@ -7587,10 +7607,10 @@
         <v>51.77</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>60.37</v>
+        <v>61.2</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>80.89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70">
@@ -7606,10 +7626,10 @@
         <v>45.09</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>49.64</v>
+        <v>50.32</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>70.43000000000001</v>
+        <v>71.39</v>
       </c>
     </row>
     <row r="71">
@@ -7625,10 +7645,10 @@
         <v>45.7</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>55.46</v>
+        <v>56.23</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>71.26000000000001</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -7644,10 +7664,10 @@
         <v>39.59</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>52.63</v>
+        <v>53.36</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>61.63</v>
+        <v>62.48</v>
       </c>
     </row>
     <row r="73">
@@ -7663,10 +7683,10 @@
         <v>38.18</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>48.63</v>
+        <v>49.3</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>59.34</v>
+        <v>60.15</v>
       </c>
     </row>
     <row r="74">
@@ -7682,10 +7702,10 @@
         <v>33.22</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.39</v>
+        <v>42.97</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>51.47</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="75">
@@ -7701,10 +7721,10 @@
         <v>29.21</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.15</v>
+        <v>35.63</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>45.11</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="76">
@@ -7720,10 +7740,10 @@
         <v>33.51</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>40.4</v>
+        <v>40.95</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>51.59</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="77">
@@ -7739,10 +7759,10 @@
         <v>35.31</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>43</v>
+        <v>43.59</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>54.27</v>
+        <v>55.01</v>
       </c>
     </row>
     <row r="78">
@@ -7758,10 +7778,10 @@
         <v>418.99</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>302.54</v>
+        <v>306.7</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>642.77</v>
+        <v>651.62</v>
       </c>
     </row>
     <row r="79">
@@ -7777,10 +7797,10 @@
         <v>29.75</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36.49</v>
+        <v>36.99</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>45.56</v>
+        <v>46.18</v>
       </c>
     </row>
     <row r="80">
@@ -7796,10 +7816,10 @@
         <v>190.57</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>148.65</v>
+        <v>150.69</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>290.93</v>
+        <v>294.93</v>
       </c>
     </row>
     <row r="81">
@@ -7815,10 +7835,10 @@
         <v>267.21</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>200.95</v>
+        <v>203.72</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>406.67</v>
+        <v>412.27</v>
       </c>
     </row>
     <row r="82">
@@ -7834,10 +7854,10 @@
         <v>27.63</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>35.78</v>
+        <v>36.27</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>41.92</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="83">
@@ -7853,10 +7873,10 @@
         <v>36.87</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>44.76</v>
+        <v>45.38</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>55.83</v>
+        <v>56.6</v>
       </c>
     </row>
     <row r="84">
@@ -7872,10 +7892,10 @@
         <v>34.27</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>45.3</v>
+        <v>45.93</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>51.79</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="85">
@@ -7891,10 +7911,10 @@
         <v>40.33</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>53.43</v>
+        <v>54.17</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>60.82</v>
+        <v>61.66</v>
       </c>
     </row>
     <row r="86">
@@ -7910,10 +7930,10 @@
         <v>32.6</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>44.05</v>
+        <v>44.66</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>49.05</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="87">
@@ -7929,10 +7949,10 @@
         <v>31.21</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>38.98</v>
+        <v>39.51</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>46.84</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="88">
@@ -7948,10 +7968,10 @@
         <v>31.03</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>37.55</v>
+        <v>38.07</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>46.46</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="89">
@@ -7967,10 +7987,10 @@
         <v>35.53</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>33.23</v>
+        <v>33.68</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>53.13</v>
+        <v>53.86</v>
       </c>
     </row>
     <row r="90">
@@ -7986,10 +8006,10 @@
         <v>30.93</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>33.71</v>
+        <v>34.17</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>46.19</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="91">
@@ -8005,10 +8025,10 @@
         <v>21.64</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>26.24</v>
+        <v>26.6</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>32.28</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="92">
@@ -8024,10 +8044,10 @@
         <v>208.38</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>153.02</v>
+        <v>155.12</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>309.21</v>
+        <v>313.46</v>
       </c>
     </row>
     <row r="93">
@@ -8043,10 +8063,10 @@
         <v>38.34</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>44.26</v>
+        <v>44.87</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>56.6</v>
+        <v>57.38</v>
       </c>
     </row>
     <row r="94">
@@ -8062,10 +8082,10 @@
         <v>27.5</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>32.86</v>
+        <v>33.31</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>40.39</v>
+        <v>40.95</v>
       </c>
     </row>
     <row r="95">
@@ -8081,10 +8101,10 @@
         <v>29.82</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>39.93</v>
+        <v>40.48</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>43.67</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="96">
@@ -8100,10 +8120,10 @@
         <v>38.76</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>49.04</v>
+        <v>49.71</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>56.58</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="97">
@@ -8119,10 +8139,10 @@
         <v>37.31</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>44.87</v>
+        <v>45.49</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>54.3</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="98">
@@ -8138,10 +8158,10 @@
         <v>42.39</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>48.11</v>
+        <v>48.77</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>61.57</v>
+        <v>62.42</v>
       </c>
     </row>
     <row r="99">
@@ -8157,10 +8177,10 @@
         <v>38.44</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>49.95</v>
+        <v>50.64</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>55.72</v>
+        <v>56.49</v>
       </c>
     </row>
     <row r="100">
@@ -8176,10 +8196,10 @@
         <v>44.12</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>54.93</v>
+        <v>55.69</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>63.83</v>
+        <v>64.70999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -8195,10 +8215,10 @@
         <v>52.46</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>58.29</v>
+        <v>59.09</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>75.90000000000001</v>
+        <v>76.94</v>
       </c>
     </row>
     <row r="102">
@@ -8214,10 +8234,10 @@
         <v>35.82</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>44.39</v>
+        <v>45</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>51.82</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="103">
@@ -8233,10 +8253,10 @@
         <v>27.64</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>34.39</v>
+        <v>34.86</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>39.99</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="104">
@@ -8252,10 +8272,10 @@
         <v>31.12</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>37.06</v>
+        <v>37.57</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>45.02</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="105">
@@ -8271,10 +8291,10 @@
         <v>31.06</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>39.27</v>
+        <v>39.81</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>44.92</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="106">
@@ -8290,10 +8310,10 @@
         <v>29.6</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>37.22</v>
+        <v>37.73</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>42.8</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="107">
@@ -8309,10 +8329,10 @@
         <v>29.99</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>42.02</v>
+        <v>42.6</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>43.29</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="108">
@@ -8328,10 +8348,10 @@
         <v>32.16</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>41.93</v>
+        <v>42.51</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>46.34</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="109">
@@ -8347,10 +8367,10 @@
         <v>42.59</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>37.67</v>
+        <v>38.19</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>61.27</v>
+        <v>62.11</v>
       </c>
     </row>
     <row r="110">
@@ -8366,10 +8386,10 @@
         <v>97.23</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>114.17</v>
+        <v>115.74</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>139.23</v>
+        <v>141.15</v>
       </c>
     </row>
     <row r="111">
@@ -8385,10 +8405,10 @@
         <v>65.08</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>90.27</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>92.77</v>
+        <v>94.05</v>
       </c>
     </row>
     <row r="112">
@@ -8404,10 +8424,10 @@
         <v>61.09</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>76.34999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>86.7</v>
+        <v>87.89</v>
       </c>
     </row>
     <row r="113">
@@ -8423,10 +8443,10 @@
         <v>55.05</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>72.26000000000001</v>
+        <v>73.25</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>78.06</v>
+        <v>79.13</v>
       </c>
     </row>
     <row r="114">
@@ -8442,10 +8462,10 @@
         <v>78.5</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>92.43000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>111.21</v>
+        <v>112.74</v>
       </c>
     </row>
     <row r="115">
@@ -8461,10 +8481,10 @@
         <v>60.95</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>75.59999999999999</v>
+        <v>76.64</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>86.28</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -8480,10 +8500,10 @@
         <v>74.05</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>83.59</v>
+        <v>84.73999999999999</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>104.7</v>
+        <v>106.14</v>
       </c>
     </row>
     <row r="117">
@@ -8499,10 +8519,10 @@
         <v>63.97</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>82.67</v>
+        <v>83.8</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>90.34999999999999</v>
+        <v>91.59</v>
       </c>
     </row>
     <row r="118">
@@ -8518,10 +8538,10 @@
         <v>67.98</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>81.34999999999999</v>
+        <v>82.45999999999999</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>95.90000000000001</v>
+        <v>97.22</v>
       </c>
     </row>
     <row r="119">
@@ -8537,10 +8557,10 @@
         <v>92.58</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>108.34</v>
+        <v>109.83</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>130.44</v>
+        <v>132.24</v>
       </c>
     </row>
     <row r="120">
@@ -8556,10 +8576,10 @@
         <v>137.04</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>153.03</v>
+        <v>155.14</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>192.84</v>
+        <v>195.5</v>
       </c>
     </row>
     <row r="121">
@@ -8575,10 +8595,10 @@
         <v>161.64</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>153.63</v>
+        <v>155.74</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>227.17</v>
+        <v>230.3</v>
       </c>
     </row>
     <row r="122">
@@ -8594,10 +8614,10 @@
         <v>80.34999999999999</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>97.48999999999999</v>
+        <v>98.83</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>112.47</v>
+        <v>114.02</v>
       </c>
     </row>
     <row r="123">
@@ -8613,10 +8633,10 @@
         <v>82.62</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>99.31999999999999</v>
+        <v>100.68</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>115.18</v>
+        <v>116.77</v>
       </c>
     </row>
     <row r="124">
@@ -8632,10 +8652,10 @@
         <v>73.02</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>85.12</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>101.39</v>
+        <v>102.78</v>
       </c>
     </row>
     <row r="125">
@@ -8651,10 +8671,10 @@
         <v>64.76000000000001</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>79.58</v>
+        <v>80.67</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>89.7</v>
+        <v>90.94</v>
       </c>
     </row>
     <row r="126">
@@ -8670,10 +8690,10 @@
         <v>54.57</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>68.83</v>
+        <v>69.78</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>75.41</v>
+        <v>76.45</v>
       </c>
     </row>
     <row r="127">
@@ -8689,10 +8709,10 @@
         <v>119</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>109.69</v>
+        <v>111.2</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>164.05</v>
+        <v>166.31</v>
       </c>
     </row>
     <row r="128">
@@ -8708,10 +8728,10 @@
         <v>137.47</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>122.27</v>
+        <v>123.96</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>189.14</v>
+        <v>191.74</v>
       </c>
     </row>
     <row r="129">
@@ -8727,10 +8747,10 @@
         <v>59.75</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>78.93000000000001</v>
+        <v>80.02</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>82.05</v>
+        <v>83.18000000000001</v>
       </c>
     </row>
     <row r="130">
@@ -8746,10 +8766,10 @@
         <v>55.71</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>67.39</v>
+        <v>68.31</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>76.34999999999999</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -8765,10 +8785,10 @@
         <v>51.23</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>65.86</v>
+        <v>66.77</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>70.09</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="132">
@@ -8784,10 +8804,10 @@
         <v>58.5</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>71</v>
+        <v>71.98</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>81</v>
       </c>
     </row>
     <row r="133">
@@ -8803,10 +8823,10 @@
         <v>59.79</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>74.20999999999999</v>
+        <v>75.23</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>81.53</v>
+        <v>82.65000000000001</v>
       </c>
     </row>
     <row r="134">
@@ -8822,10 +8842,10 @@
         <v>60.81</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>70.48</v>
+        <v>71.45</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>82.8</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="135">
@@ -8841,10 +8861,10 @@
         <v>50.71</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>56.65</v>
+        <v>57.43</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>68.95</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -8860,10 +8880,10 @@
         <v>49.36</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>55.75</v>
+        <v>56.52</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>67.02</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="137">
@@ -8879,10 +8899,10 @@
         <v>34.86</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>43.45</v>
+        <v>44.05</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>47.31</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="138">
@@ -8898,10 +8918,10 @@
         <v>35.52</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>44.37</v>
+        <v>44.98</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>48.17</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="139">
@@ -8917,10 +8937,10 @@
         <v>31.78</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>38.82</v>
+        <v>39.35</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>43.07</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="140">
@@ -8936,10 +8956,10 @@
         <v>47.98</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>46.97</v>
+        <v>47.62</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>64.98999999999999</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="141">
@@ -8955,10 +8975,10 @@
         <v>49.24</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>60.71</v>
+        <v>61.54</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>66.65000000000001</v>
+        <v>67.56999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8974,10 +8994,10 @@
         <v>34.48</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>38.61</v>
+        <v>39.14</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>46.64</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="143">
@@ -8993,10 +9013,10 @@
         <v>49.75</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>53.91</v>
+        <v>54.66</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>67.14</v>
+        <v>68.06</v>
       </c>
     </row>
     <row r="144">
@@ -9012,10 +9032,10 @@
         <v>43.01</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>51.19</v>
+        <v>51.89</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>57.91</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="145">
@@ -9031,10 +9051,10 @@
         <v>87.84</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>78.72</v>
+        <v>79.81</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>117.98</v>
+        <v>119.61</v>
       </c>
     </row>
     <row r="146">
@@ -9050,10 +9070,10 @@
         <v>105.03</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>98.61</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>140.89</v>
+        <v>142.83</v>
       </c>
     </row>
     <row r="147">
@@ -9069,10 +9089,10 @@
         <v>64.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>81.31999999999999</v>
+        <v>82.44</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>86.77</v>
+        <v>87.95999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -9088,10 +9108,10 @@
         <v>72.77</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>79.03</v>
+        <v>80.12</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>97.36</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="149">
@@ -9107,10 +9127,10 @@
         <v>51.88</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>54.92</v>
+        <v>55.67</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>69.31999999999999</v>
+        <v>70.28</v>
       </c>
     </row>
     <row r="150">
@@ -9126,10 +9146,10 @@
         <v>63.99</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>65.23</v>
+        <v>66.13</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>85.40000000000001</v>
+        <v>86.56999999999999</v>
       </c>
     </row>
     <row r="151">
@@ -9145,10 +9165,10 @@
         <v>97.42</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>89.06999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>129.84</v>
+        <v>131.63</v>
       </c>
     </row>
     <row r="152">
@@ -9164,10 +9184,10 @@
         <v>71.81</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>67.03</v>
+        <v>67.95</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>95.77</v>
+        <v>97.09</v>
       </c>
     </row>
     <row r="153">
@@ -9183,10 +9203,10 @@
         <v>53.34</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>54.34</v>
+        <v>55.09</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>71.19</v>
+        <v>72.17</v>
       </c>
     </row>
     <row r="154">
@@ -9202,10 +9222,10 @@
         <v>73.59</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>73.89</v>
+        <v>74.91</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>98.28</v>
+        <v>99.63</v>
       </c>
     </row>
     <row r="155">
@@ -9221,10 +9241,10 @@
         <v>63.34</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>66.09999999999999</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>84.45999999999999</v>
+        <v>85.63</v>
       </c>
     </row>
     <row r="156">
@@ -9240,10 +9260,10 @@
         <v>101.4</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>94.14</v>
+        <v>95.44</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>135.02</v>
+        <v>136.88</v>
       </c>
     </row>
     <row r="157">
@@ -9259,10 +9279,10 @@
         <v>162.44</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>163.68</v>
+        <v>165.93</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>215.98</v>
+        <v>218.95</v>
       </c>
     </row>
     <row r="158">
@@ -9278,10 +9298,10 @@
         <v>376.22</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>304.29</v>
+        <v>308.48</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>499.06</v>
+        <v>505.93</v>
       </c>
     </row>
     <row r="159">
@@ -9297,10 +9317,10 @@
         <v>86.52</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>87.66</v>
+        <v>88.87</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>114.5</v>
+        <v>116.08</v>
       </c>
     </row>
     <row r="160">
@@ -9316,10 +9336,10 @@
         <v>70.70999999999999</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>79.02</v>
+        <v>80.11</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>93.36</v>
+        <v>94.65000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -9335,10 +9355,10 @@
         <v>71.86</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>78.11</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>94.70999999999999</v>
+        <v>96.02</v>
       </c>
     </row>
     <row r="162">
@@ -9354,10 +9374,10 @@
         <v>81.73999999999999</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>81.43000000000001</v>
+        <v>82.55</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>107.55</v>
+        <v>109.03</v>
       </c>
     </row>
     <row r="163">
@@ -9373,10 +9393,10 @@
         <v>92.59</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>127.8</v>
+        <v>129.55</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>121.61</v>
+        <v>123.28</v>
       </c>
     </row>
     <row r="164">
@@ -9392,10 +9412,10 @@
         <v>102.67</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>110.5</v>
+        <v>112.02</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>134.64</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="165">
@@ -9411,10 +9431,10 @@
         <v>298.82</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>235.5</v>
+        <v>238.74</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>391.28</v>
+        <v>396.67</v>
       </c>
     </row>
     <row r="166">
@@ -9430,10 +9450,10 @@
         <v>164.54</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>160.03</v>
+        <v>162.23</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>215.13</v>
+        <v>218.09</v>
       </c>
     </row>
     <row r="167">
@@ -9449,10 +9469,10 @@
         <v>140.44</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>156.39</v>
+        <v>158.54</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>183.5</v>
+        <v>186.02</v>
       </c>
     </row>
     <row r="168">
@@ -9468,10 +9488,10 @@
         <v>134.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>155.58</v>
+        <v>157.72</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>175.73</v>
+        <v>178.14</v>
       </c>
     </row>
     <row r="169">
@@ -9487,10 +9507,10 @@
         <v>113.03</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>142.01</v>
+        <v>143.96</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>147.49</v>
+        <v>149.52</v>
       </c>
     </row>
     <row r="170">
@@ -9506,10 +9526,10 @@
         <v>127.48</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>147.78</v>
+        <v>149.81</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>166.01</v>
+        <v>168.29</v>
       </c>
     </row>
     <row r="171">
@@ -9525,10 +9545,10 @@
         <v>126.76</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>136.95</v>
+        <v>138.84</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>164.74</v>
+        <v>167</v>
       </c>
     </row>
     <row r="172">
@@ -9544,10 +9564,10 @@
         <v>80.16</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>95.44</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>103.96</v>
+        <v>105.39</v>
       </c>
     </row>
     <row r="173">
@@ -9563,10 +9583,10 @@
         <v>76.89</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>89.76000000000001</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>99.5</v>
+        <v>100.87</v>
       </c>
     </row>
     <row r="174">
@@ -9582,10 +9602,10 @@
         <v>110.15</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>117.14</v>
+        <v>118.75</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>142.22</v>
+        <v>144.18</v>
       </c>
     </row>
     <row r="175">
@@ -9601,10 +9621,10 @@
         <v>93.62</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>107.59</v>
+        <v>109.07</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>120.61</v>
+        <v>122.27</v>
       </c>
     </row>
     <row r="176">
@@ -9620,10 +9640,10 @@
         <v>231.26</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>204.23</v>
+        <v>207.04</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>297.5</v>
+        <v>301.59</v>
       </c>
     </row>
     <row r="177">
@@ -9639,10 +9659,10 @@
         <v>143.22</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>140.24</v>
+        <v>142.16</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>183.97</v>
+        <v>186.51</v>
       </c>
     </row>
     <row r="178">
@@ -9658,10 +9678,10 @@
         <v>89.47</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>103.51</v>
+        <v>104.94</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>114.76</v>
+        <v>116.34</v>
       </c>
     </row>
     <row r="179">
@@ -9677,10 +9697,10 @@
         <v>134.3</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>126.03</v>
+        <v>127.76</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>172.06</v>
+        <v>174.43</v>
       </c>
     </row>
     <row r="180">
@@ -9696,10 +9716,10 @@
         <v>105.82</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>113.26</v>
+        <v>114.82</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>135.41</v>
+        <v>137.27</v>
       </c>
     </row>
     <row r="181">
@@ -9715,10 +9735,10 @@
         <v>125.64</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>135.38</v>
+        <v>137.24</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>160.58</v>
+        <v>162.79</v>
       </c>
     </row>
     <row r="182">
@@ -9734,10 +9754,10 @@
         <v>147.26</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>134.99</v>
+        <v>136.85</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>187.95</v>
+        <v>190.53</v>
       </c>
     </row>
     <row r="183">
@@ -9753,10 +9773,10 @@
         <v>89.47</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>92.16</v>
+        <v>93.42</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>114.02</v>
+        <v>115.59</v>
       </c>
     </row>
     <row r="184">
@@ -9772,10 +9792,10 @@
         <v>102.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>115.3</v>
+        <v>116.88</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>130.51</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="185">
@@ -9791,10 +9811,10 @@
         <v>105.22</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>124.65</v>
+        <v>126.37</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>133.67</v>
+        <v>135.51</v>
       </c>
     </row>
     <row r="186">
@@ -9810,10 +9830,10 @@
         <v>102.27</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>125.26</v>
+        <v>126.98</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>129.7</v>
+        <v>131.48</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9849,10 @@
         <v>111.5</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>116.96</v>
+        <v>118.56</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>141.16</v>
+        <v>143.1</v>
       </c>
     </row>
     <row r="188">
@@ -9848,10 +9868,10 @@
         <v>407.47</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>305.15</v>
+        <v>309.35</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>515.89</v>
+        <v>522.99</v>
       </c>
     </row>
     <row r="189">
@@ -9867,10 +9887,10 @@
         <v>117.28</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>140.2</v>
+        <v>142.13</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>148.49</v>
+        <v>150.53</v>
       </c>
     </row>
     <row r="190">
@@ -9886,10 +9906,10 @@
         <v>175.2</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>166.63</v>
+        <v>168.92</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>221.84</v>
+        <v>224.89</v>
       </c>
     </row>
     <row r="191">
@@ -9905,10 +9925,10 @@
         <v>97.14</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>118.58</v>
+        <v>120.22</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>122.75</v>
+        <v>124.44</v>
       </c>
     </row>
     <row r="192">
@@ -9924,10 +9944,10 @@
         <v>92.58</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>107.03</v>
+        <v>108.5</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>116.76</v>
+        <v>118.37</v>
       </c>
     </row>
     <row r="193">
@@ -9943,10 +9963,10 @@
         <v>113.86</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>120.46</v>
+        <v>122.12</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>143.32</v>
+        <v>145.29</v>
       </c>
     </row>
     <row r="194">
@@ -9962,10 +9982,10 @@
         <v>92.31999999999999</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>92.88</v>
+        <v>94.16</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>115.99</v>
+        <v>117.58</v>
       </c>
     </row>
     <row r="195">
@@ -9981,10 +10001,10 @@
         <v>99.59</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>98.79000000000001</v>
+        <v>100.15</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>124.89</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="196">
@@ -10000,10 +10020,10 @@
         <v>81.09999999999999</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>91.31</v>
+        <v>92.56</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>101.51</v>
+        <v>102.91</v>
       </c>
     </row>
     <row r="197">
@@ -10019,10 +10039,10 @@
         <v>69.06999999999999</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>84.09</v>
+        <v>85.25</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>86.25</v>
+        <v>87.44</v>
       </c>
     </row>
     <row r="198">
@@ -10038,10 +10058,10 @@
         <v>34.58</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>63.37</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>43.09</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="199">
@@ -10057,10 +10077,10 @@
         <v>123.62</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>104.46</v>
+        <v>105.9</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>153.67</v>
+        <v>155.79</v>
       </c>
     </row>
     <row r="200">
@@ -10076,10 +10096,10 @@
         <v>124.39</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>103.3</v>
+        <v>104.72</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>154.44</v>
+        <v>156.57</v>
       </c>
     </row>
     <row r="201">
@@ -10095,10 +10115,10 @@
         <v>75.56</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>79.59</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>93.7</v>
+        <v>94.98999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10114,10 +10134,10 @@
         <v>64.53</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>58.15</v>
+        <v>58.95</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>79.92</v>
+        <v>81.02</v>
       </c>
     </row>
     <row r="203">
@@ -10133,10 +10153,10 @@
         <v>40.07</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>41.76</v>
+        <v>42.33</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>49.95</v>
+        <v>50.64</v>
       </c>
     </row>
     <row r="204">
@@ -10152,10 +10172,10 @@
         <v>44.77</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>46.75</v>
+        <v>47.39</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>56.17</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="205">
@@ -10171,10 +10191,10 @@
         <v>64.04000000000001</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>63.48</v>
+        <v>64.36</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>80.87</v>
+        <v>81.98</v>
       </c>
     </row>
     <row r="206">
@@ -10190,10 +10210,10 @@
         <v>68.84999999999999</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>74.54000000000001</v>
+        <v>75.56</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>86.5</v>
+        <v>87.69</v>
       </c>
     </row>
     <row r="207">
@@ -10209,10 +10229,10 @@
         <v>56.61</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>56.96</v>
+        <v>57.74</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>70.76000000000001</v>
+        <v>71.73</v>
       </c>
     </row>
     <row r="208">
@@ -10228,10 +10248,10 @@
         <v>7.52</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>18.91</v>
+        <v>19.18</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>9.35</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="209">
@@ -10247,10 +10267,10 @@
         <v>40.23</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>40.88</v>
+        <v>41.44</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>49.88</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="210">
@@ -10266,10 +10286,10 @@
         <v>37.9</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>45.39</v>
+        <v>46.01</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>46.85</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="211">
@@ -10285,10 +10305,10 @@
         <v>10.26</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>20.68</v>
+        <v>20.96</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>12.64</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="212">
@@ -10304,10 +10324,10 @@
         <v>12.41</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>35.3</v>
+        <v>35.79</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>15.27</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="213">
@@ -10323,10 +10343,10 @@
         <v>25.88</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>27.61</v>
+        <v>27.99</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>31.77</v>
+        <v>32.21</v>
       </c>
     </row>
     <row r="214">
@@ -10342,10 +10362,10 @@
         <v>82.06999999999999</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>84.27</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>100.57</v>
+        <v>101.95</v>
       </c>
     </row>
     <row r="215">
@@ -10361,10 +10381,10 @@
         <v>62.15</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>63.73</v>
+        <v>64.61</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>75.97</v>
+        <v>77.02</v>
       </c>
     </row>
     <row r="216">
@@ -10380,10 +10400,10 @@
         <v>111.31</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>89</v>
+        <v>90.23</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>135.73</v>
+        <v>137.6</v>
       </c>
     </row>
     <row r="217">
@@ -10399,10 +10419,10 @@
         <v>96.95999999999999</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>102.66</v>
+        <v>104.07</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>117.95</v>
+        <v>119.57</v>
       </c>
     </row>
     <row r="218">
@@ -10418,10 +10438,10 @@
         <v>117.5</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>110.61</v>
+        <v>112.14</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>142.53</v>
+        <v>144.49</v>
       </c>
     </row>
     <row r="219">
@@ -10437,10 +10457,10 @@
         <v>46.43</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>52.54</v>
+        <v>53.27</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>56.16</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="220">
@@ -10456,10 +10476,10 @@
         <v>18.34</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>22.64</v>
+        <v>22.95</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>22.12</v>
+        <v>22.43</v>
       </c>
     </row>
     <row r="221">
@@ -10475,10 +10495,10 @@
         <v>9.65</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>17.46</v>
+        <v>17.7</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>11.59</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="222">
@@ -10494,10 +10514,10 @@
         <v>43.67</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>45.08</v>
+        <v>45.7</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>52.23</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="223">
@@ -10513,10 +10533,10 @@
         <v>93.66</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>83.75</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>111.55</v>
+        <v>113.09</v>
       </c>
     </row>
     <row r="224">
@@ -10532,10 +10552,10 @@
         <v>120.28</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>105.17</v>
+        <v>106.62</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>142.23</v>
+        <v>144.19</v>
       </c>
     </row>
     <row r="225">
@@ -10551,10 +10571,10 @@
         <v>44.11</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>63.66</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>51.79</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="226">
@@ -10570,10 +10590,10 @@
         <v>68.09</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>78.11</v>
+        <v>79.19</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>79.38</v>
+        <v>80.47</v>
       </c>
     </row>
     <row r="227">
@@ -10589,10 +10609,10 @@
         <v>168.67</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>176.57</v>
+        <v>179</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>195.48</v>
+        <v>198.16</v>
       </c>
     </row>
     <row r="228">
@@ -10608,10 +10628,10 @@
         <v>403.15</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>359.8</v>
+        <v>364.75</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>464.46</v>
+        <v>470.85</v>
       </c>
     </row>
     <row r="229">
@@ -10627,10 +10647,10 @@
         <v>349.33</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>346.57</v>
+        <v>351.33</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>400.1</v>
+        <v>405.6</v>
       </c>
     </row>
     <row r="230">
@@ -10646,10 +10666,10 @@
         <v>489.22</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>424.03</v>
+        <v>429.86</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>556.91</v>
+        <v>564.5700000000001</v>
       </c>
     </row>
     <row r="231">
@@ -10665,10 +10685,10 @@
         <v>226.62</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>195.79</v>
+        <v>198.48</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>256.41</v>
+        <v>259.94</v>
       </c>
     </row>
     <row r="232">
@@ -10684,10 +10704,10 @@
         <v>137.68</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>166.27</v>
+        <v>168.56</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>154.84</v>
+        <v>156.97</v>
       </c>
     </row>
     <row r="233">
@@ -10703,10 +10723,10 @@
         <v>68.95</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>104.5</v>
+        <v>105.94</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>77.06999999999999</v>
+        <v>78.13</v>
       </c>
     </row>
     <row r="234">
@@ -10722,10 +10742,10 @@
         <v>55.1</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>69.45</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>61.21</v>
+        <v>62.06</v>
       </c>
     </row>
     <row r="235">
@@ -10741,10 +10761,10 @@
         <v>14.86</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>39.12</v>
+        <v>39.66</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>16.41</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="236">
@@ -10760,10 +10780,10 @@
         <v>41.16</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>62.88</v>
+        <v>63.74</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>45.25</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="237">
@@ -10779,10 +10799,10 @@
         <v>130.19</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>106.21</v>
+        <v>107.67</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>142.47</v>
+        <v>144.43</v>
       </c>
     </row>
     <row r="238">
@@ -10798,10 +10818,10 @@
         <v>54.46</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>70.73</v>
+        <v>71.7</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>59.33</v>
+        <v>60.15</v>
       </c>
     </row>
     <row r="239">
@@ -10817,10 +10837,10 @@
         <v>81.17</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>92.36</v>
+        <v>93.63</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>88.18000000000001</v>
+        <v>89.39</v>
       </c>
     </row>
     <row r="240">
@@ -10836,10 +10856,10 @@
         <v>236.79</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>214.81</v>
+        <v>217.76</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>256.51</v>
+        <v>260.04</v>
       </c>
     </row>
     <row r="241">
@@ -10855,10 +10875,10 @@
         <v>125.95</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>92.45999999999999</v>
+        <v>93.73</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>136.05</v>
+        <v>137.93</v>
       </c>
     </row>
     <row r="242">
@@ -10874,10 +10894,10 @@
         <v>94.95999999999999</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>78.3</v>
+        <v>79.37</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>102.19</v>
+        <v>103.59</v>
       </c>
     </row>
     <row r="243">
@@ -10893,10 +10913,10 @@
         <v>216.23</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>171.8</v>
+        <v>174.16</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>231.8</v>
+        <v>234.98</v>
       </c>
     </row>
     <row r="244">
@@ -10912,10 +10932,10 @@
         <v>34.35</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>44.13</v>
+        <v>44.73</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>36.68</v>
+        <v>37.19</v>
       </c>
     </row>
     <row r="245">
@@ -10931,10 +10951,10 @@
         <v>9.57</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>16.11</v>
+        <v>16.33</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>10.2</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="246">
@@ -10950,10 +10970,10 @@
         <v>48.53</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>47.77</v>
+        <v>48.43</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>51.61</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="247">
@@ -10969,10 +10989,10 @@
         <v>45.54</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>40.36</v>
+        <v>40.91</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>48.33</v>
+        <v>48.99</v>
       </c>
     </row>
     <row r="248">
@@ -10988,10 +11008,10 @@
         <v>23.49</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>34.64</v>
+        <v>35.11</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>24.85</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="249">
@@ -11007,10 +11027,10 @@
         <v>74.73999999999999</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>69.68000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>78.83</v>
+        <v>79.91</v>
       </c>
     </row>
     <row r="250">
@@ -11026,10 +11046,10 @@
         <v>70.23999999999999</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>70.58</v>
+        <v>71.56</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>73.84999999999999</v>
+        <v>74.87</v>
       </c>
     </row>
     <row r="251">
@@ -11045,10 +11065,10 @@
         <v>81.98999999999999</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>96.92</v>
+        <v>98.25</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>85.91</v>
+        <v>87.09</v>
       </c>
     </row>
     <row r="252">
@@ -11064,10 +11084,10 @@
         <v>143.45</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>141.7</v>
+        <v>143.65</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>149.79</v>
+        <v>151.85</v>
       </c>
     </row>
     <row r="253">
@@ -11083,10 +11103,10 @@
         <v>212.87</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>183.85</v>
+        <v>186.37</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>221.5</v>
+        <v>224.55</v>
       </c>
     </row>
     <row r="254">
@@ -11102,10 +11122,10 @@
         <v>295.38</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>250.82</v>
+        <v>254.27</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>307.14</v>
+        <v>311.36</v>
       </c>
     </row>
     <row r="255">
@@ -11121,10 +11141,10 @@
         <v>219.7</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>155.36</v>
+        <v>157.5</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>228.28</v>
+        <v>231.42</v>
       </c>
     </row>
     <row r="256">
@@ -11140,10 +11160,10 @@
         <v>144.76</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>83.36</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>150.3</v>
+        <v>152.37</v>
       </c>
     </row>
     <row r="257">
@@ -11159,10 +11179,10 @@
         <v>29.04</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>36.57</v>
+        <v>37.07</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>30.13</v>
+        <v>30.55</v>
       </c>
     </row>
     <row r="258">
@@ -11178,10 +11198,10 @@
         <v>49.02</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>63.16</v>
+        <v>64.03</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>50.83</v>
+        <v>51.53</v>
       </c>
     </row>
     <row r="259">
@@ -11197,10 +11217,10 @@
         <v>47.42</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>63.7</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>49.14</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="260">
@@ -11216,10 +11236,10 @@
         <v>8.76</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>49.82</v>
+        <v>50.5</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>9.050000000000001</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="261">
@@ -11235,10 +11255,10 @@
         <v>87.75</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>94.08</v>
+        <v>95.37</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>90.38</v>
+        <v>91.62</v>
       </c>
     </row>
     <row r="262">
@@ -11254,10 +11274,10 @@
         <v>55.45</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>63.45</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>56.94</v>
+        <v>57.72</v>
       </c>
     </row>
     <row r="263">
@@ -11273,10 +11293,10 @@
         <v>82.23</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>90.98</v>
+        <v>92.23</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>84.23</v>
+        <v>85.38</v>
       </c>
     </row>
     <row r="264">
@@ -11292,10 +11312,10 @@
         <v>93.44</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>85.12</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>95.47</v>
+        <v>96.78</v>
       </c>
     </row>
     <row r="265">
@@ -11311,10 +11331,10 @@
         <v>424.64</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>255.21</v>
+        <v>258.72</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>432.79</v>
+        <v>438.75</v>
       </c>
     </row>
     <row r="266">
@@ -11330,10 +11350,10 @@
         <v>223.67</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>167.38</v>
+        <v>169.68</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>226.97</v>
+        <v>230.09</v>
       </c>
     </row>
     <row r="267">
@@ -11349,10 +11369,10 @@
         <v>84.67</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>87.76000000000001</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>85.54000000000001</v>
+        <v>86.72</v>
       </c>
     </row>
     <row r="268">
@@ -11368,10 +11388,10 @@
         <v>57.7</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>57.94</v>
+        <v>58.74</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>58.04</v>
+        <v>58.84</v>
       </c>
     </row>
     <row r="269">
@@ -11387,10 +11407,10 @@
         <v>40.14</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>50.37</v>
+        <v>51.06</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>40.3</v>
+        <v>40.85</v>
       </c>
     </row>
     <row r="270">
@@ -11406,10 +11426,10 @@
         <v>9.94</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>32.54</v>
+        <v>32.99</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>9.960000000000001</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="271">
@@ -11425,10 +11445,10 @@
         <v>-0.41</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>27.92</v>
+        <v>28.3</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="272">
@@ -11444,10 +11464,10 @@
         <v>250.71</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>152.25</v>
+        <v>153.64</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>250.71</v>
+        <v>253</v>
       </c>
     </row>
     <row r="273">
@@ -11463,10 +11483,10 @@
         <v>34.52</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>56</v>
+        <v>56.25</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>34.52</v>
+        <v>34.68</v>
       </c>
     </row>
     <row r="274">
@@ -11507,8 +11527,27 @@
         <v>58.97</v>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="B276" s="5" t="n">
+        <v>55.79</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="D276" s="5" t="n">
+        <v>55.79</v>
+      </c>
+      <c r="E276" s="5" t="n">
+        <v>59.52</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B275">
+  <conditionalFormatting sqref="B2:B276">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11520,7 +11559,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C275">
+  <conditionalFormatting sqref="C2:C276">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11532,7 +11571,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D275">
+  <conditionalFormatting sqref="D2:D276">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11544,7 +11583,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E275">
+  <conditionalFormatting sqref="E2:E276">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/SA_historical_prices.xlsx
+++ b/outputs/SA_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>86.11</v>
+        <v>68.91</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>106.66</v>
+        <v>74.64</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>87.75</v>
+        <v>69.86</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>108.91</v>
+        <v>75.72</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>92.17</v>
+        <v>86.64</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>108.57</v>
+        <v>101.39</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>95.42</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>112.47</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>85.12</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>99.3</v>
+        <v>96.92</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>89.08</v>
+        <v>87.7</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>103.98</v>
+        <v>101.28</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>96.48999999999999</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>111.51</v>
+        <v>110.57</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>106.01</v>
+        <v>105.01</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>122.58</v>
+        <v>121.26</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>90.90000000000001</v>
+        <v>90.25</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>109.35</v>
+        <v>108.34</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>108.35</v>
+        <v>107.34</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>130.88</v>
+        <v>129.39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: May 2026</t>
+          <t>Data through: Jun 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6273,6 +6273,26 @@
       </c>
       <c r="F276" s="7" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="F277" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6284,7 +6304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E276"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11546,8 +11566,27 @@
         <v>59.52</v>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Jun 2026</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="D277" s="5" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="E277" s="5" t="n">
+        <v>40.45</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B276">
+  <conditionalFormatting sqref="B2:B277">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11559,7 +11598,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C276">
+  <conditionalFormatting sqref="C2:C277">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11571,7 +11610,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D276">
+  <conditionalFormatting sqref="D2:D277">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11583,7 +11622,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E276">
+  <conditionalFormatting sqref="E2:E277">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/SA_historical_prices.xlsx
+++ b/outputs/SA_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>68.91</v>
+        <v>61.83</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>74.64</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>69.86</v>
+        <v>62.39</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>75.72</v>
+        <v>65.55</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>86.64</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>101.39</v>
+        <v>93.58</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>89.48999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>104.8</v>
+        <v>96.31999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>83.95999999999999</v>
+        <v>84.16</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>96.92</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>87.7</v>
+        <v>87.72</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>101.28</v>
+        <v>101.4</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>95.81999999999999</v>
+        <v>95.63</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>110.57</v>
+        <v>110.41</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>105.01</v>
+        <v>104.47</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>121.26</v>
+        <v>120.65</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>90.25</v>
+        <v>89</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>108.34</v>
+        <v>106.1</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>107.34</v>
+        <v>105.43</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>129.39</v>
+        <v>126.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jun 2026</t>
+          <t>Data through: Jul 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F277"/>
+  <dimension ref="A1:F278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6293,6 +6293,26 @@
       </c>
       <c r="F277" s="7" t="inlineStr"/>
     </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="F278" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6304,7 +6324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11585,8 +11605,27 @@
         <v>40.45</v>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Jul 2026</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="D278" s="5" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="E278" s="5" t="n">
+        <v>108.02</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B277">
+  <conditionalFormatting sqref="B2:B278">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11598,7 +11637,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C277">
+  <conditionalFormatting sqref="C2:C278">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11610,7 +11649,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D277">
+  <conditionalFormatting sqref="D2:D278">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11622,7 +11661,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E277">
+  <conditionalFormatting sqref="E2:E278">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>

--- a/outputs/SA_historical_prices.xlsx
+++ b/outputs/SA_historical_prices.xlsx
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>61.83</v>
+        <v>60.72</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>65.01000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>62.39</v>
+        <v>61.34</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>65.55</v>
+        <v>66.22</v>
       </c>
     </row>
     <row r="6">
@@ -547,16 +547,16 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>79.93000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>93.58</v>
+        <v>88.25</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>82.23</v>
+        <v>79.13</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>96.31999999999999</v>
+        <v>90.98</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>84.16</v>
+        <v>81.75</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>97.29000000000001</v>
+        <v>93.83</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>87.72</v>
+        <v>85.39</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>101.4</v>
+        <v>97.95999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>95.63</v>
+        <v>96.13</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>110.41</v>
+        <v>111.17</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>104.47</v>
+        <v>105.41</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>120.65</v>
+        <v>121.93</v>
       </c>
     </row>
     <row r="9">
@@ -604,22 +604,22 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>89</v>
+        <v>89.06</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>106.1</v>
+        <v>106.15</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>105.43</v>
+        <v>105.93</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>126.08</v>
+        <v>126.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Data through: Jul 2026</t>
+          <t>Data through: Aug 2026</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F278"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -690,10 +690,10 @@
         <v>34.07</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>50.33</v>
+        <v>50.63</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>63.32</v>
+        <v>63.7</v>
       </c>
       <c r="F2" s="7" t="inlineStr"/>
     </row>
@@ -710,10 +710,10 @@
         <v>26.44</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>42.29</v>
+        <v>42.55</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>49.04</v>
+        <v>49.34</v>
       </c>
       <c r="F3" s="7" t="inlineStr"/>
     </row>
@@ -730,10 +730,10 @@
         <v>27.77</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>43.05</v>
+        <v>43.3</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>51.41</v>
+        <v>51.72</v>
       </c>
       <c r="F4" s="7" t="inlineStr"/>
     </row>
@@ -750,10 +750,10 @@
         <v>29.25</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>46.45</v>
+        <v>46.72</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>54.06</v>
+        <v>54.38</v>
       </c>
       <c r="F5" s="7" t="inlineStr"/>
     </row>
@@ -770,10 +770,10 @@
         <v>50.3</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>59.98</v>
+        <v>60.34</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>92.8</v>
+        <v>93.36</v>
       </c>
       <c r="F6" s="7" t="inlineStr"/>
     </row>
@@ -790,10 +790,10 @@
         <v>43.98</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>56.65</v>
+        <v>56.99</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>81</v>
+        <v>81.48</v>
       </c>
       <c r="F7" s="7" t="inlineStr"/>
     </row>
@@ -810,10 +810,10 @@
         <v>37.22</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>60.12</v>
+        <v>60.48</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>68.34999999999999</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="F8" s="7" t="inlineStr"/>
     </row>
@@ -830,10 +830,10 @@
         <v>108.46</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>158.98</v>
+        <v>159.93</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>198.58</v>
+        <v>199.77</v>
       </c>
       <c r="F9" s="7" t="inlineStr"/>
     </row>
@@ -850,10 +850,10 @@
         <v>64.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>76.22</v>
+        <v>76.67</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>117.51</v>
+        <v>118.21</v>
       </c>
       <c r="F10" s="7" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
         <v>37.5</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>57.49</v>
+        <v>57.83</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>68.34999999999999</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="F11" s="7" t="inlineStr"/>
     </row>
@@ -890,10 +890,10 @@
         <v>40.38</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>62.02</v>
+        <v>62.39</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>73.48999999999999</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="F12" s="7" t="inlineStr"/>
     </row>
@@ -910,10 +910,10 @@
         <v>36.85</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>59.18</v>
+        <v>59.54</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>66.95999999999999</v>
+        <v>67.36</v>
       </c>
       <c r="F13" s="7" t="inlineStr"/>
     </row>
@@ -930,10 +930,10 @@
         <v>50.28</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>71.64</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>91.23999999999999</v>
+        <v>91.78</v>
       </c>
       <c r="F14" s="7" t="inlineStr"/>
     </row>
@@ -950,10 +950,10 @@
         <v>33.56</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>58.66</v>
+        <v>59.01</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>60.81</v>
+        <v>61.18</v>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
     </row>
@@ -970,10 +970,10 @@
         <v>34.17</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>55.59</v>
+        <v>55.92</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>61.83</v>
+        <v>62.21</v>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
     </row>
@@ -990,10 +990,10 @@
         <v>54.24</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>74.45999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>97.90000000000001</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
     </row>
@@ -1010,10 +1010,10 @@
         <v>94.34999999999999</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>116.83</v>
+        <v>117.53</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>169.87</v>
+        <v>170.89</v>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
     </row>
@@ -1030,10 +1030,10 @@
         <v>40.24</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>60.65</v>
+        <v>61.01</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>72.27</v>
+        <v>72.7</v>
       </c>
       <c r="F19" s="7" t="inlineStr"/>
     </row>
@@ -1050,10 +1050,10 @@
         <v>41.25</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>55.14</v>
+        <v>55.47</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>73.91</v>
+        <v>74.36</v>
       </c>
       <c r="F20" s="7" t="inlineStr"/>
     </row>
@@ -1070,10 +1070,10 @@
         <v>32.11</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>46.48</v>
+        <v>46.76</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>57.41</v>
+        <v>57.75</v>
       </c>
       <c r="F21" s="7" t="inlineStr"/>
     </row>
@@ -1090,10 +1090,10 @@
         <v>43.91</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>56.85</v>
+        <v>57.19</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>78.33</v>
+        <v>78.8</v>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
     </row>
@@ -1110,10 +1110,10 @@
         <v>42.74</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>62.9</v>
+        <v>63.28</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>76.09</v>
+        <v>76.55</v>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
     </row>
@@ -1130,10 +1130,10 @@
         <v>46.01</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>67.34</v>
+        <v>67.75</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>81.75</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
     </row>
@@ -1150,10 +1150,10 @@
         <v>32.96</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>49.56</v>
+        <v>49.86</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>58.45</v>
+        <v>58.8</v>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
     </row>
@@ -1170,10 +1170,10 @@
         <v>37.36</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>54.42</v>
+        <v>54.75</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>66.03</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
     </row>
@@ -1190,10 +1190,10 @@
         <v>43.61</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>58.45</v>
+        <v>58.8</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>76.83</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
     </row>
@@ -1210,10 +1210,10 @@
         <v>38.81</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>55.03</v>
+        <v>55.36</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>68.15000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
     </row>
@@ -1230,10 +1230,10 @@
         <v>37.79</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>52.85</v>
+        <v>53.17</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>66.23999999999999</v>
+        <v>66.64</v>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
     </row>
@@ -1250,10 +1250,10 @@
         <v>64.09</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>71.08</v>
+        <v>71.5</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>112.15</v>
+        <v>112.82</v>
       </c>
       <c r="F30" s="7" t="inlineStr"/>
     </row>
@@ -1270,10 +1270,10 @@
         <v>71.84999999999999</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>81.38</v>
+        <v>81.87</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>125.51</v>
+        <v>126.26</v>
       </c>
       <c r="F31" s="7" t="inlineStr"/>
     </row>
@@ -1290,10 +1290,10 @@
         <v>109.21</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>126.65</v>
+        <v>127.41</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>190.23</v>
+        <v>191.37</v>
       </c>
       <c r="F32" s="7" t="inlineStr"/>
     </row>
@@ -1310,10 +1310,10 @@
         <v>48.02</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>54.68</v>
+        <v>55</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>83.40000000000001</v>
+        <v>83.91</v>
       </c>
       <c r="F33" s="7" t="inlineStr"/>
     </row>
@@ -1330,10 +1330,10 @@
         <v>36.24</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>51.27</v>
+        <v>51.57</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>62.77</v>
+        <v>63.14</v>
       </c>
       <c r="F34" s="7" t="inlineStr"/>
     </row>
@@ -1350,10 +1350,10 @@
         <v>33.95</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>48.05</v>
+        <v>48.34</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>58.49</v>
+        <v>58.84</v>
       </c>
       <c r="F35" s="7" t="inlineStr"/>
     </row>
@@ -1370,10 +1370,10 @@
         <v>52.72</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>66.09</v>
+        <v>66.48</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>90.34999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F36" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>47.94</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>66.87</v>
+        <v>67.27</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>81.73999999999999</v>
+        <v>82.23</v>
       </c>
       <c r="F37" s="7" t="inlineStr"/>
     </row>
@@ -1410,10 +1410,10 @@
         <v>70.05</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>84.73999999999999</v>
+        <v>85.25</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>119.08</v>
+        <v>119.79</v>
       </c>
       <c r="F38" s="7" t="inlineStr"/>
     </row>
@@ -1430,10 +1430,10 @@
         <v>42.93</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>63.81</v>
+        <v>64.2</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>72.76000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="F39" s="7" t="inlineStr"/>
     </row>
@@ -1450,10 +1450,10 @@
         <v>38.55</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>53.45</v>
+        <v>53.77</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>65.15000000000001</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="F40" s="7" t="inlineStr"/>
     </row>
@@ -1470,10 +1470,10 @@
         <v>36.13</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>49.38</v>
+        <v>49.68</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>61.08</v>
+        <v>61.45</v>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
     </row>
@@ -1490,10 +1490,10 @@
         <v>44.26</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>61.48</v>
+        <v>61.85</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>74.84999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="F42" s="7" t="inlineStr"/>
     </row>
@@ -1510,10 +1510,10 @@
         <v>57.46</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>65.45999999999999</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>97.22</v>
+        <v>97.8</v>
       </c>
       <c r="F43" s="7" t="inlineStr"/>
     </row>
@@ -1530,10 +1530,10 @@
         <v>111.81</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>112.46</v>
+        <v>113.14</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>189.12</v>
+        <v>190.25</v>
       </c>
       <c r="F44" s="7" t="inlineStr"/>
     </row>
@@ -1550,10 +1550,10 @@
         <v>75.23999999999999</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>89.23</v>
+        <v>89.77</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>127.23</v>
+        <v>127.99</v>
       </c>
       <c r="F45" s="7" t="inlineStr"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>69.39</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>82.11</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>117.3</v>
+        <v>118.01</v>
       </c>
       <c r="F46" s="7" t="inlineStr"/>
     </row>
@@ -1590,10 +1590,10 @@
         <v>82.88</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>117.5</v>
+        <v>118.2</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>139.54</v>
+        <v>140.37</v>
       </c>
       <c r="F47" s="7" t="inlineStr"/>
     </row>
@@ -1610,10 +1610,10 @@
         <v>70.90000000000001</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>95.47</v>
+        <v>96.05</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>118.88</v>
+        <v>119.59</v>
       </c>
       <c r="F48" s="7" t="inlineStr"/>
     </row>
@@ -1630,10 +1630,10 @@
         <v>133.72</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>171.39</v>
+        <v>172.42</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>223.31</v>
+        <v>224.65</v>
       </c>
       <c r="F49" s="7" t="inlineStr"/>
     </row>
@@ -1650,10 +1650,10 @@
         <v>113.89</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>142.6</v>
+        <v>143.46</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>189.75</v>
+        <v>190.89</v>
       </c>
       <c r="F50" s="7" t="inlineStr"/>
     </row>
@@ -1670,10 +1670,10 @@
         <v>50.5</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>69.15000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>83.95</v>
+        <v>84.45</v>
       </c>
       <c r="F51" s="7" t="inlineStr"/>
     </row>
@@ -1690,10 +1690,10 @@
         <v>53.16</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>71.55</v>
+        <v>71.98</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>88.17</v>
+        <v>88.7</v>
       </c>
       <c r="F52" s="7" t="inlineStr"/>
     </row>
@@ -1710,10 +1710,10 @@
         <v>43.35</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>58.12</v>
+        <v>58.47</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>71.67</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F53" s="7" t="inlineStr"/>
     </row>
@@ -1730,10 +1730,10 @@
         <v>54.39</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>69.29000000000001</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>89.65000000000001</v>
+        <v>90.19</v>
       </c>
       <c r="F54" s="7" t="inlineStr"/>
     </row>
@@ -1750,10 +1750,10 @@
         <v>63.76</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>75.13</v>
+        <v>75.58</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>104.77</v>
+        <v>105.4</v>
       </c>
       <c r="F55" s="7" t="inlineStr"/>
     </row>
@@ -1770,10 +1770,10 @@
         <v>226.68</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>197.03</v>
+        <v>198.21</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>370.83</v>
+        <v>373.06</v>
       </c>
       <c r="F56" s="7" t="inlineStr"/>
     </row>
@@ -1790,10 +1790,10 @@
         <v>248.69</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>206.19</v>
+        <v>207.43</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>405.04</v>
+        <v>407.47</v>
       </c>
       <c r="F57" s="7" t="inlineStr"/>
     </row>
@@ -1810,10 +1810,10 @@
         <v>450.11</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>337.53</v>
+        <v>339.55</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>729.85</v>
+        <v>734.23</v>
       </c>
       <c r="F58" s="7" t="inlineStr"/>
     </row>
@@ -1830,10 +1830,10 @@
         <v>51.23</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>67.42</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>82.67</v>
+        <v>83.17</v>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
     </row>
@@ -1850,10 +1850,10 @@
         <v>60.14</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>96.58</v>
+        <v>97.16</v>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
     </row>
@@ -1870,10 +1870,10 @@
         <v>48.05</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>64.11</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>76.8</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
     </row>
@@ -1890,10 +1890,10 @@
         <v>60.06</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>69.23</v>
+        <v>69.64</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>95.62</v>
+        <v>96.2</v>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
     </row>
@@ -1910,10 +1910,10 @@
         <v>50.93</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>65.42</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>80.78</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
     </row>
@@ -1930,10 +1930,10 @@
         <v>40.83</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>49.82</v>
+        <v>50.11</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>64.51000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
     </row>
@@ -1950,10 +1950,10 @@
         <v>45.57</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>56.26</v>
+        <v>56.6</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>72.08</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
     </row>
@@ -1970,10 +1970,10 @@
         <v>43.01</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>50.73</v>
+        <v>51.04</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>68.09999999999999</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
     </row>
@@ -1990,10 +1990,10 @@
         <v>29.77</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>38.88</v>
+        <v>39.12</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>47.19</v>
+        <v>47.47</v>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
     </row>
@@ -2010,10 +2010,10 @@
         <v>475</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>362.3</v>
+        <v>364.47</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>752.65</v>
+        <v>757.16</v>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
     </row>
@@ -2030,10 +2030,10 @@
         <v>51.77</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>82</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
     </row>
@@ -2050,10 +2050,10 @@
         <v>45.09</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>50.32</v>
+        <v>50.62</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>71.39</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
     </row>
@@ -2070,10 +2070,10 @@
         <v>45.7</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>56.23</v>
+        <v>56.56</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>72.23999999999999</v>
+        <v>72.67</v>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>39.59</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>53.36</v>
+        <v>53.68</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>62.48</v>
+        <v>62.85</v>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
     </row>
@@ -2110,10 +2110,10 @@
         <v>38.18</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>49.3</v>
+        <v>49.59</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>60.15</v>
+        <v>60.51</v>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
     </row>
@@ -2130,10 +2130,10 @@
         <v>33.22</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.97</v>
+        <v>43.23</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>52.17</v>
+        <v>52.49</v>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
     </row>
@@ -2150,10 +2150,10 @@
         <v>29.21</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.63</v>
+        <v>35.85</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>45.73</v>
+        <v>46.01</v>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>33.51</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>40.95</v>
+        <v>41.2</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>52.3</v>
+        <v>52.62</v>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
     </row>
@@ -2190,10 +2190,10 @@
         <v>35.31</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>43.59</v>
+        <v>43.85</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>55.01</v>
+        <v>55.34</v>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
     </row>
@@ -2210,10 +2210,10 @@
         <v>418.99</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>306.7</v>
+        <v>308.54</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>651.62</v>
+        <v>655.52</v>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
     </row>
@@ -2230,10 +2230,10 @@
         <v>29.75</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36.99</v>
+        <v>37.22</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>46.18</v>
+        <v>46.46</v>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
     </row>
@@ -2250,10 +2250,10 @@
         <v>190.57</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>150.69</v>
+        <v>151.6</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>294.93</v>
+        <v>296.7</v>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
     </row>
@@ -2270,10 +2270,10 @@
         <v>267.21</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>203.72</v>
+        <v>204.94</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>412.27</v>
+        <v>414.74</v>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
     </row>
@@ -2290,10 +2290,10 @@
         <v>27.63</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>36.27</v>
+        <v>36.49</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>42.5</v>
+        <v>42.75</v>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
     </row>
@@ -2310,10 +2310,10 @@
         <v>36.87</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>45.38</v>
+        <v>45.65</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>56.6</v>
+        <v>56.94</v>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
     </row>
@@ -2330,10 +2330,10 @@
         <v>34.27</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>45.93</v>
+        <v>46.2</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>52.5</v>
+        <v>52.81</v>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
     </row>
@@ -2350,10 +2350,10 @@
         <v>40.33</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>54.17</v>
+        <v>54.49</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>61.66</v>
+        <v>62.03</v>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
     </row>
@@ -2370,10 +2370,10 @@
         <v>32.6</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>44.66</v>
+        <v>44.93</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>49.72</v>
+        <v>50.02</v>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
     </row>
@@ -2390,10 +2390,10 @@
         <v>31.21</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>39.51</v>
+        <v>39.75</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>47.49</v>
+        <v>47.77</v>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
     </row>
@@ -2410,10 +2410,10 @@
         <v>31.03</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>38.07</v>
+        <v>38.3</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>47.1</v>
+        <v>47.38</v>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
     </row>
@@ -2430,10 +2430,10 @@
         <v>35.53</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>33.68</v>
+        <v>33.89</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>53.86</v>
+        <v>54.18</v>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
     </row>
@@ -2450,10 +2450,10 @@
         <v>30.93</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>34.17</v>
+        <v>34.38</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>46.83</v>
+        <v>47.11</v>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
     </row>
@@ -2470,10 +2470,10 @@
         <v>21.64</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>26.6</v>
+        <v>26.76</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>32.72</v>
+        <v>32.92</v>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
     </row>
@@ -2490,10 +2490,10 @@
         <v>208.38</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>155.12</v>
+        <v>156.05</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>313.46</v>
+        <v>315.34</v>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
     </row>
@@ -2510,10 +2510,10 @@
         <v>38.34</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>44.87</v>
+        <v>45.14</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>57.38</v>
+        <v>57.72</v>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
     </row>
@@ -2530,10 +2530,10 @@
         <v>27.5</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>33.31</v>
+        <v>33.51</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>40.95</v>
+        <v>41.19</v>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
     </row>
@@ -2550,10 +2550,10 @@
         <v>29.82</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>40.48</v>
+        <v>40.72</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>44.27</v>
+        <v>44.53</v>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
     </row>
@@ -2570,10 +2570,10 @@
         <v>38.76</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>49.71</v>
+        <v>50.01</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>57.36</v>
+        <v>57.71</v>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
     </row>
@@ -2590,10 +2590,10 @@
         <v>37.31</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>45.49</v>
+        <v>45.76</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>55.05</v>
+        <v>55.38</v>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
     </row>
@@ -2610,10 +2610,10 @@
         <v>42.39</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>48.77</v>
+        <v>49.06</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>62.42</v>
+        <v>62.79</v>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
     </row>
@@ -2630,10 +2630,10 @@
         <v>38.44</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>50.64</v>
+        <v>50.95</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>56.49</v>
+        <v>56.83</v>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
     </row>
@@ -2650,10 +2650,10 @@
         <v>44.12</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>55.69</v>
+        <v>56.02</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>64.70999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
     </row>
@@ -2670,10 +2670,10 @@
         <v>52.46</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>59.09</v>
+        <v>59.45</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>76.94</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
     </row>
@@ -2690,10 +2690,10 @@
         <v>35.82</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>45</v>
+        <v>45.27</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>52.54</v>
+        <v>52.85</v>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
     </row>
@@ -2710,10 +2710,10 @@
         <v>27.64</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>34.86</v>
+        <v>35.07</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>40.54</v>
+        <v>40.78</v>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
     </row>
@@ -2730,10 +2730,10 @@
         <v>31.12</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>37.57</v>
+        <v>37.79</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>45.63</v>
+        <v>45.91</v>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
     </row>
@@ -2750,10 +2750,10 @@
         <v>31.06</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>39.81</v>
+        <v>40.04</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>45.54</v>
+        <v>45.81</v>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
     </row>
@@ -2770,10 +2770,10 @@
         <v>29.6</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>37.73</v>
+        <v>37.96</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>43.39</v>
+        <v>43.65</v>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
     </row>
@@ -2790,10 +2790,10 @@
         <v>29.99</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>42.6</v>
+        <v>42.85</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>43.88</v>
+        <v>44.15</v>
       </c>
       <c r="F107" s="7" t="inlineStr"/>
     </row>
@@ -2810,10 +2810,10 @@
         <v>32.16</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>42.51</v>
+        <v>42.76</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>46.98</v>
+        <v>47.26</v>
       </c>
       <c r="F108" s="7" t="inlineStr"/>
     </row>
@@ -2830,10 +2830,10 @@
         <v>42.59</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>38.19</v>
+        <v>38.42</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>62.11</v>
+        <v>62.48</v>
       </c>
       <c r="F109" s="7" t="inlineStr"/>
     </row>
@@ -2850,10 +2850,10 @@
         <v>97.23</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>115.74</v>
+        <v>116.44</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>141.15</v>
+        <v>141.99</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
@@ -2874,10 +2874,10 @@
         <v>65.08</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>91.51000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>94.05</v>
+        <v>94.61</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
@@ -2898,10 +2898,10 @@
         <v>61.09</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>77.40000000000001</v>
+        <v>77.87</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>87.89</v>
+        <v>88.42</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
         <v>55.05</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>73.25</v>
+        <v>73.69</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>79.13</v>
+        <v>79.61</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         <v>78.5</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>93.7</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>112.74</v>
+        <v>113.42</v>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
@@ -2970,10 +2970,10 @@
         <v>60.95</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>76.64</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>87.45999999999999</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="F115" s="10" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         <v>74.05</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>84.73999999999999</v>
+        <v>85.25</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>106.14</v>
+        <v>106.78</v>
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
         <v>63.97</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>83.8</v>
+        <v>84.31</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>91.59</v>
+        <v>92.14</v>
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
@@ -3042,10 +3042,10 @@
         <v>67.98</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>82.45999999999999</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="E118" s="9" t="n">
-        <v>97.22</v>
+        <v>97.81</v>
       </c>
       <c r="F118" s="10" t="inlineStr">
         <is>
@@ -3066,10 +3066,10 @@
         <v>92.58</v>
       </c>
       <c r="D119" s="9" t="n">
-        <v>109.83</v>
+        <v>110.49</v>
       </c>
       <c r="E119" s="9" t="n">
-        <v>132.24</v>
+        <v>133.03</v>
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
@@ -3090,10 +3090,10 @@
         <v>137.04</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>155.14</v>
+        <v>156.07</v>
       </c>
       <c r="E120" s="9" t="n">
-        <v>195.5</v>
+        <v>196.67</v>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         <v>161.64</v>
       </c>
       <c r="D121" s="9" t="n">
-        <v>155.74</v>
+        <v>156.68</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>230.3</v>
+        <v>231.68</v>
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
@@ -3138,10 +3138,10 @@
         <v>80.34999999999999</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>98.83</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>114.02</v>
+        <v>114.7</v>
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
@@ -3162,10 +3162,10 @@
         <v>82.62</v>
       </c>
       <c r="D123" s="9" t="n">
-        <v>100.68</v>
+        <v>101.29</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>116.77</v>
+        <v>117.47</v>
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         <v>73.02</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>86.29000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>102.78</v>
+        <v>103.4</v>
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>64.76000000000001</v>
       </c>
       <c r="D125" s="9" t="n">
-        <v>80.67</v>
+        <v>81.16</v>
       </c>
       <c r="E125" s="9" t="n">
-        <v>90.94</v>
+        <v>91.48</v>
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         <v>54.57</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>69.78</v>
+        <v>70.2</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>76.45</v>
+        <v>76.91</v>
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
@@ -3258,10 +3258,10 @@
         <v>119</v>
       </c>
       <c r="D127" s="9" t="n">
-        <v>111.2</v>
+        <v>111.87</v>
       </c>
       <c r="E127" s="9" t="n">
-        <v>166.31</v>
+        <v>167.31</v>
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
         <v>137.47</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>123.96</v>
+        <v>124.7</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>191.74</v>
+        <v>192.89</v>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
@@ -3306,10 +3306,10 @@
         <v>59.75</v>
       </c>
       <c r="D129" s="9" t="n">
-        <v>80.02</v>
+        <v>80.5</v>
       </c>
       <c r="E129" s="9" t="n">
-        <v>83.18000000000001</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
@@ -3330,10 +3330,10 @@
         <v>55.71</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>68.31</v>
+        <v>68.72</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>77.40000000000001</v>
+        <v>77.86</v>
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         <v>51.23</v>
       </c>
       <c r="D131" s="9" t="n">
-        <v>66.77</v>
+        <v>67.17</v>
       </c>
       <c r="E131" s="9" t="n">
-        <v>71.06</v>
+        <v>71.48</v>
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         <v>58.5</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>71.98</v>
+        <v>72.41</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>81</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
         <v>59.79</v>
       </c>
       <c r="D133" s="9" t="n">
-        <v>75.23</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="E133" s="9" t="n">
-        <v>82.65000000000001</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         <v>60.81</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>71.45</v>
+        <v>71.88</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>83.94</v>
+        <v>84.45</v>
       </c>
       <c r="F134" s="7" t="inlineStr"/>
     </row>
@@ -3446,10 +3446,10 @@
         <v>50.71</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>57.43</v>
+        <v>57.77</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="F135" s="7" t="inlineStr"/>
     </row>
@@ -3466,10 +3466,10 @@
         <v>49.36</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>56.52</v>
+        <v>56.86</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>67.95</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="F136" s="7" t="inlineStr"/>
     </row>
@@ -3486,10 +3486,10 @@
         <v>34.86</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>44.05</v>
+        <v>44.31</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>47.96</v>
+        <v>48.24</v>
       </c>
       <c r="F137" s="7" t="inlineStr"/>
     </row>
@@ -3506,10 +3506,10 @@
         <v>35.52</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>44.98</v>
+        <v>45.25</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>48.83</v>
+        <v>49.13</v>
       </c>
       <c r="F138" s="7" t="inlineStr"/>
     </row>
@@ -3526,10 +3526,10 @@
         <v>31.78</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>39.35</v>
+        <v>39.59</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>43.66</v>
+        <v>43.93</v>
       </c>
       <c r="F139" s="7" t="inlineStr"/>
     </row>
@@ -3546,10 +3546,10 @@
         <v>47.98</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>47.62</v>
+        <v>47.9</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>65.88</v>
+        <v>66.28</v>
       </c>
       <c r="F140" s="7" t="inlineStr"/>
     </row>
@@ -3566,10 +3566,10 @@
         <v>49.24</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>61.54</v>
+        <v>61.91</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>67.56999999999999</v>
+        <v>67.97</v>
       </c>
       <c r="F141" s="7" t="inlineStr"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>34.48</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>39.14</v>
+        <v>39.37</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>47.28</v>
+        <v>47.57</v>
       </c>
       <c r="F142" s="7" t="inlineStr"/>
     </row>
@@ -3606,10 +3606,10 @@
         <v>49.75</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>54.66</v>
+        <v>54.98</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>68.06</v>
+        <v>68.47</v>
       </c>
       <c r="F143" s="7" t="inlineStr"/>
     </row>
@@ -3626,10 +3626,10 @@
         <v>43.01</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>51.89</v>
+        <v>52.2</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>58.7</v>
+        <v>59.05</v>
       </c>
       <c r="F144" s="7" t="inlineStr"/>
     </row>
@@ -3646,10 +3646,10 @@
         <v>87.84</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>79.81</v>
+        <v>80.28</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>119.61</v>
+        <v>120.32</v>
       </c>
       <c r="F145" s="7" t="inlineStr"/>
     </row>
@@ -3666,10 +3666,10 @@
         <v>105.03</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>99.95999999999999</v>
+        <v>100.56</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>142.83</v>
+        <v>143.68</v>
       </c>
       <c r="F146" s="7" t="inlineStr"/>
     </row>
@@ -3686,10 +3686,10 @@
         <v>64.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>82.44</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="F147" s="7" t="inlineStr"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>72.77</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>80.12</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>98.7</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="F148" s="7" t="inlineStr"/>
     </row>
@@ -3726,10 +3726,10 @@
         <v>51.88</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>55.67</v>
+        <v>56.01</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>70.28</v>
+        <v>70.7</v>
       </c>
       <c r="F149" s="7" t="inlineStr"/>
     </row>
@@ -3746,10 +3746,10 @@
         <v>63.99</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>66.13</v>
+        <v>66.53</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>86.56999999999999</v>
+        <v>87.09</v>
       </c>
       <c r="F150" s="7" t="inlineStr"/>
     </row>
@@ -3766,10 +3766,10 @@
         <v>97.42</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>90.3</v>
+        <v>90.84</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>131.63</v>
+        <v>132.42</v>
       </c>
       <c r="F151" s="7" t="inlineStr"/>
     </row>
@@ -3786,10 +3786,10 @@
         <v>71.81</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>67.95</v>
+        <v>68.36</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>97.09</v>
+        <v>97.67</v>
       </c>
       <c r="F152" s="7" t="inlineStr"/>
     </row>
@@ -3806,10 +3806,10 @@
         <v>53.34</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>55.09</v>
+        <v>55.42</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>72.17</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F153" s="7" t="inlineStr"/>
     </row>
@@ -3826,10 +3826,10 @@
         <v>73.59</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>74.91</v>
+        <v>75.36</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>99.63</v>
+        <v>100.23</v>
       </c>
       <c r="F154" s="7" t="inlineStr"/>
     </row>
@@ -3846,10 +3846,10 @@
         <v>63.34</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>67.01000000000001</v>
+        <v>67.41</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>85.63</v>
+        <v>86.14</v>
       </c>
       <c r="F155" s="7" t="inlineStr"/>
     </row>
@@ -3866,10 +3866,10 @@
         <v>101.4</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>95.44</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>136.88</v>
+        <v>137.7</v>
       </c>
       <c r="F156" s="7" t="inlineStr"/>
     </row>
@@ -3886,10 +3886,10 @@
         <v>162.44</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>165.93</v>
+        <v>166.92</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>218.95</v>
+        <v>220.27</v>
       </c>
       <c r="F157" s="7" t="inlineStr"/>
     </row>
@@ -3906,10 +3906,10 @@
         <v>376.22</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>308.48</v>
+        <v>310.33</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>505.93</v>
+        <v>508.96</v>
       </c>
       <c r="F158" s="7" t="inlineStr"/>
     </row>
@@ -3926,10 +3926,10 @@
         <v>86.52</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>88.87</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>116.08</v>
+        <v>116.77</v>
       </c>
       <c r="F159" s="7" t="inlineStr"/>
     </row>
@@ -3946,10 +3946,10 @@
         <v>70.70999999999999</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>80.11</v>
+        <v>80.59</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>94.65000000000001</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="F160" s="7" t="inlineStr"/>
     </row>
@@ -3966,10 +3966,10 @@
         <v>71.86</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>79.18000000000001</v>
+        <v>79.66</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>96.02</v>
+        <v>96.59</v>
       </c>
       <c r="F161" s="7" t="inlineStr"/>
     </row>
@@ -3986,10 +3986,10 @@
         <v>81.73999999999999</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>82.55</v>
+        <v>83.05</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>109.03</v>
+        <v>109.68</v>
       </c>
       <c r="F162" s="7" t="inlineStr"/>
     </row>
@@ -4006,10 +4006,10 @@
         <v>92.59</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>129.55</v>
+        <v>130.33</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>123.28</v>
+        <v>124.02</v>
       </c>
       <c r="F163" s="7" t="inlineStr"/>
     </row>
@@ -4026,10 +4026,10 @@
         <v>102.67</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>112.02</v>
+        <v>112.69</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>136.5</v>
+        <v>137.32</v>
       </c>
       <c r="F164" s="7" t="inlineStr"/>
     </row>
@@ -4046,10 +4046,10 @@
         <v>298.82</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>238.74</v>
+        <v>240.17</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>396.67</v>
+        <v>399.05</v>
       </c>
       <c r="F165" s="7" t="inlineStr"/>
     </row>
@@ -4066,10 +4066,10 @@
         <v>164.54</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>162.23</v>
+        <v>163.21</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>218.09</v>
+        <v>219.39</v>
       </c>
       <c r="F166" s="7" t="inlineStr"/>
     </row>
@@ -4086,10 +4086,10 @@
         <v>140.44</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>158.54</v>
+        <v>159.49</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>186.02</v>
+        <v>187.14</v>
       </c>
       <c r="F167" s="7" t="inlineStr"/>
     </row>
@@ -4106,10 +4106,10 @@
         <v>134.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>157.72</v>
+        <v>158.67</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>178.14</v>
+        <v>179.21</v>
       </c>
       <c r="F168" s="7" t="inlineStr"/>
     </row>
@@ -4126,10 +4126,10 @@
         <v>113.03</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>143.96</v>
+        <v>144.83</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>149.52</v>
+        <v>150.42</v>
       </c>
       <c r="F169" s="7" t="inlineStr"/>
     </row>
@@ -4146,10 +4146,10 @@
         <v>127.48</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>149.81</v>
+        <v>150.71</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>168.29</v>
+        <v>169.3</v>
       </c>
       <c r="F170" s="7" t="inlineStr"/>
     </row>
@@ -4166,10 +4166,10 @@
         <v>126.76</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>138.84</v>
+        <v>139.67</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F171" s="7" t="inlineStr"/>
     </row>
@@ -4186,10 +4186,10 @@
         <v>80.16</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>96.76000000000001</v>
+        <v>97.34</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>105.39</v>
+        <v>106.03</v>
       </c>
       <c r="F172" s="7" t="inlineStr"/>
     </row>
@@ -4206,10 +4206,10 @@
         <v>76.89</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>90.98999999999999</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>100.87</v>
+        <v>101.47</v>
       </c>
       <c r="F173" s="7" t="inlineStr"/>
     </row>
@@ -4226,10 +4226,10 @@
         <v>110.15</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>118.75</v>
+        <v>119.46</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>144.18</v>
+        <v>145.04</v>
       </c>
       <c r="F174" s="7" t="inlineStr"/>
     </row>
@@ -4246,10 +4246,10 @@
         <v>93.62</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>109.07</v>
+        <v>109.72</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>122.27</v>
+        <v>123</v>
       </c>
       <c r="F175" s="7" t="inlineStr"/>
     </row>
@@ -4266,10 +4266,10 @@
         <v>231.26</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>207.04</v>
+        <v>208.28</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>301.59</v>
+        <v>303.4</v>
       </c>
       <c r="F176" s="7" t="inlineStr"/>
     </row>
@@ -4286,10 +4286,10 @@
         <v>143.22</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>142.16</v>
+        <v>143.02</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>186.51</v>
+        <v>187.62</v>
       </c>
       <c r="F177" s="7" t="inlineStr"/>
     </row>
@@ -4306,10 +4306,10 @@
         <v>89.47</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>104.94</v>
+        <v>105.57</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>116.34</v>
+        <v>117.04</v>
       </c>
       <c r="F178" s="7" t="inlineStr"/>
     </row>
@@ -4326,10 +4326,10 @@
         <v>134.3</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>127.76</v>
+        <v>128.53</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>174.43</v>
+        <v>175.47</v>
       </c>
       <c r="F179" s="7" t="inlineStr"/>
     </row>
@@ -4346,10 +4346,10 @@
         <v>105.82</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>114.82</v>
+        <v>115.51</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>137.27</v>
+        <v>138.1</v>
       </c>
       <c r="F180" s="7" t="inlineStr"/>
     </row>
@@ -4366,10 +4366,10 @@
         <v>125.64</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>137.24</v>
+        <v>138.06</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>162.79</v>
+        <v>163.77</v>
       </c>
       <c r="F181" s="7" t="inlineStr"/>
     </row>
@@ -4386,10 +4386,10 @@
         <v>147.26</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>136.85</v>
+        <v>137.67</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>190.53</v>
+        <v>191.67</v>
       </c>
       <c r="F182" s="7" t="inlineStr"/>
     </row>
@@ -4406,10 +4406,10 @@
         <v>89.47</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>93.42</v>
+        <v>93.98</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>115.59</v>
+        <v>116.29</v>
       </c>
       <c r="F183" s="7" t="inlineStr"/>
     </row>
@@ -4426,10 +4426,10 @@
         <v>102.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>116.88</v>
+        <v>117.59</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>132.3</v>
+        <v>133.1</v>
       </c>
       <c r="F184" s="7" t="inlineStr"/>
     </row>
@@ -4446,10 +4446,10 @@
         <v>105.22</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>126.37</v>
+        <v>127.13</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>135.51</v>
+        <v>136.32</v>
       </c>
       <c r="F185" s="7" t="inlineStr"/>
     </row>
@@ -4466,10 +4466,10 @@
         <v>102.27</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>126.98</v>
+        <v>127.75</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>131.48</v>
+        <v>132.27</v>
       </c>
       <c r="F186" s="7" t="inlineStr"/>
     </row>
@@ -4486,10 +4486,10 @@
         <v>111.5</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>118.56</v>
+        <v>119.28</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>143.1</v>
+        <v>143.96</v>
       </c>
       <c r="F187" s="7" t="inlineStr"/>
     </row>
@@ -4506,10 +4506,10 @@
         <v>407.47</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>309.35</v>
+        <v>311.2</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>522.99</v>
+        <v>526.12</v>
       </c>
       <c r="F188" s="7" t="inlineStr"/>
     </row>
@@ -4526,10 +4526,10 @@
         <v>117.28</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>142.13</v>
+        <v>142.98</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>150.53</v>
+        <v>151.44</v>
       </c>
       <c r="F189" s="7" t="inlineStr"/>
     </row>
@@ -4546,10 +4546,10 @@
         <v>175.2</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>168.92</v>
+        <v>169.94</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>224.89</v>
+        <v>226.24</v>
       </c>
       <c r="F190" s="7" t="inlineStr"/>
     </row>
@@ -4566,10 +4566,10 @@
         <v>97.14</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>120.22</v>
+        <v>120.94</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>124.44</v>
+        <v>125.19</v>
       </c>
       <c r="F191" s="7" t="inlineStr"/>
     </row>
@@ -4586,10 +4586,10 @@
         <v>92.58</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>108.5</v>
+        <v>109.15</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>118.37</v>
+        <v>119.08</v>
       </c>
       <c r="F192" s="7" t="inlineStr"/>
     </row>
@@ -4606,10 +4606,10 @@
         <v>113.86</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>122.12</v>
+        <v>122.85</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>145.29</v>
+        <v>146.16</v>
       </c>
       <c r="F193" s="7" t="inlineStr"/>
     </row>
@@ -4626,10 +4626,10 @@
         <v>92.31999999999999</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>94.16</v>
+        <v>94.72</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>117.58</v>
+        <v>118.29</v>
       </c>
       <c r="F194" s="7" t="inlineStr"/>
     </row>
@@ -4646,10 +4646,10 @@
         <v>99.59</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>100.15</v>
+        <v>100.75</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>126.6</v>
+        <v>127.36</v>
       </c>
       <c r="F195" s="7" t="inlineStr"/>
     </row>
@@ -4666,10 +4666,10 @@
         <v>81.09999999999999</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>92.56</v>
+        <v>93.12</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>102.91</v>
+        <v>103.52</v>
       </c>
       <c r="F196" s="7" t="inlineStr"/>
     </row>
@@ -4686,10 +4686,10 @@
         <v>69.06999999999999</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>85.25</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>87.44</v>
+        <v>87.97</v>
       </c>
       <c r="F197" s="7" t="inlineStr"/>
     </row>
@@ -4706,10 +4706,10 @@
         <v>34.58</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>64.23999999999999</v>
+        <v>64.63</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
       <c r="F198" s="7" t="inlineStr"/>
     </row>
@@ -4726,10 +4726,10 @@
         <v>123.62</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>105.9</v>
+        <v>106.53</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>155.79</v>
+        <v>156.72</v>
       </c>
       <c r="F199" s="7" t="inlineStr"/>
     </row>
@@ -4746,10 +4746,10 @@
         <v>124.39</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>104.72</v>
+        <v>105.35</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>156.57</v>
+        <v>157.5</v>
       </c>
       <c r="F200" s="7" t="inlineStr"/>
     </row>
@@ -4766,10 +4766,10 @@
         <v>75.56</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>80.68000000000001</v>
+        <v>81.17</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>94.98999999999999</v>
+        <v>95.56</v>
       </c>
       <c r="F201" s="7" t="inlineStr"/>
     </row>
@@ -4786,10 +4786,10 @@
         <v>64.53</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>58.95</v>
+        <v>59.3</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>81.02</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="F202" s="7" t="inlineStr"/>
     </row>
@@ -4806,10 +4806,10 @@
         <v>40.07</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>42.33</v>
+        <v>42.59</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>50.64</v>
+        <v>50.94</v>
       </c>
       <c r="F203" s="7" t="inlineStr"/>
     </row>
@@ -4826,10 +4826,10 @@
         <v>44.77</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>47.39</v>
+        <v>47.67</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>56.94</v>
+        <v>57.28</v>
       </c>
       <c r="F204" s="7" t="inlineStr"/>
     </row>
@@ -4846,10 +4846,10 @@
         <v>64.04000000000001</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>64.36</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>81.98</v>
+        <v>82.48</v>
       </c>
       <c r="F205" s="7" t="inlineStr"/>
     </row>
@@ -4866,10 +4866,10 @@
         <v>68.84999999999999</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>75.56</v>
+        <v>76.02</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>87.69</v>
+        <v>88.22</v>
       </c>
       <c r="F206" s="7" t="inlineStr"/>
     </row>
@@ -4886,10 +4886,10 @@
         <v>56.61</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>57.74</v>
+        <v>58.09</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>71.73</v>
+        <v>72.16</v>
       </c>
       <c r="F207" s="7" t="inlineStr"/>
     </row>
@@ -4906,10 +4906,10 @@
         <v>7.52</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>19.18</v>
+        <v>19.29</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>9.48</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F208" s="7" t="inlineStr"/>
     </row>
@@ -4926,10 +4926,10 @@
         <v>40.23</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>41.44</v>
+        <v>41.69</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>50.57</v>
+        <v>50.87</v>
       </c>
       <c r="F209" s="7" t="inlineStr"/>
     </row>
@@ -4946,10 +4946,10 @@
         <v>37.9</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>46.01</v>
+        <v>46.29</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>47.49</v>
+        <v>47.78</v>
       </c>
       <c r="F210" s="7" t="inlineStr"/>
     </row>
@@ -4966,10 +4966,10 @@
         <v>10.26</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>20.96</v>
+        <v>21.09</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>12.82</v>
+        <v>12.9</v>
       </c>
       <c r="F211" s="7" t="inlineStr"/>
     </row>
@@ -4986,10 +4986,10 @@
         <v>12.41</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>35.79</v>
+        <v>36</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>15.48</v>
+        <v>15.57</v>
       </c>
       <c r="F212" s="7" t="inlineStr"/>
     </row>
@@ -5006,10 +5006,10 @@
         <v>25.88</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>27.99</v>
+        <v>28.16</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>32.21</v>
+        <v>32.4</v>
       </c>
       <c r="F213" s="7" t="inlineStr"/>
     </row>
@@ -5026,10 +5026,10 @@
         <v>82.06999999999999</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>85.43000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>101.95</v>
+        <v>102.56</v>
       </c>
       <c r="F214" s="7" t="inlineStr"/>
     </row>
@@ -5046,10 +5046,10 @@
         <v>62.15</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>64.61</v>
+        <v>65</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>77.02</v>
+        <v>77.48</v>
       </c>
       <c r="F215" s="7" t="inlineStr"/>
     </row>
@@ -5066,10 +5066,10 @@
         <v>111.31</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>90.23</v>
+        <v>90.77</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>137.6</v>
+        <v>138.42</v>
       </c>
       <c r="F216" s="7" t="inlineStr"/>
     </row>
@@ -5086,10 +5086,10 @@
         <v>96.95999999999999</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>104.07</v>
+        <v>104.69</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>119.57</v>
+        <v>120.29</v>
       </c>
       <c r="F217" s="7" t="inlineStr"/>
     </row>
@@ -5106,10 +5106,10 @@
         <v>117.5</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>112.14</v>
+        <v>112.81</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>144.49</v>
+        <v>145.36</v>
       </c>
       <c r="F218" s="7" t="inlineStr"/>
     </row>
@@ -5126,10 +5126,10 @@
         <v>46.43</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>53.27</v>
+        <v>53.59</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>56.93</v>
+        <v>57.28</v>
       </c>
       <c r="F219" s="7" t="inlineStr"/>
     </row>
@@ -5146,10 +5146,10 @@
         <v>18.34</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>22.95</v>
+        <v>23.09</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>22.43</v>
+        <v>22.56</v>
       </c>
       <c r="F220" s="7" t="inlineStr"/>
     </row>
@@ -5166,10 +5166,10 @@
         <v>9.65</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>17.7</v>
+        <v>17.81</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>11.75</v>
+        <v>11.82</v>
       </c>
       <c r="F221" s="7" t="inlineStr"/>
     </row>
@@ -5186,10 +5186,10 @@
         <v>43.67</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>45.7</v>
+        <v>45.97</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>52.95</v>
+        <v>53.27</v>
       </c>
       <c r="F222" s="7" t="inlineStr"/>
     </row>
@@ -5206,10 +5206,10 @@
         <v>93.66</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>84.90000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>113.09</v>
+        <v>113.76</v>
       </c>
       <c r="F223" s="7" t="inlineStr"/>
     </row>
@@ -5226,10 +5226,10 @@
         <v>120.28</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>106.62</v>
+        <v>107.26</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>144.19</v>
+        <v>145.05</v>
       </c>
       <c r="F224" s="7" t="inlineStr"/>
     </row>
@@ -5246,10 +5246,10 @@
         <v>44.11</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>64.54000000000001</v>
+        <v>64.92</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>52.5</v>
+        <v>52.82</v>
       </c>
       <c r="F225" s="7" t="inlineStr"/>
     </row>
@@ -5266,10 +5266,10 @@
         <v>68.09</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>79.19</v>
+        <v>79.66</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>80.47</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="F226" s="7" t="inlineStr"/>
     </row>
@@ -5286,10 +5286,10 @@
         <v>168.67</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>179</v>
+        <v>180.08</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>198.16</v>
+        <v>199.35</v>
       </c>
       <c r="F227" s="7" t="inlineStr"/>
     </row>
@@ -5306,10 +5306,10 @@
         <v>403.15</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>364.75</v>
+        <v>366.93</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>470.85</v>
+        <v>473.68</v>
       </c>
       <c r="F228" s="7" t="inlineStr"/>
     </row>
@@ -5326,10 +5326,10 @@
         <v>349.33</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>351.33</v>
+        <v>353.44</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>405.6</v>
+        <v>408.04</v>
       </c>
       <c r="F229" s="7" t="inlineStr"/>
     </row>
@@ -5346,10 +5346,10 @@
         <v>489.22</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>429.86</v>
+        <v>432.44</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>564.5700000000001</v>
+        <v>567.96</v>
       </c>
       <c r="F230" s="7" t="inlineStr"/>
     </row>
@@ -5366,10 +5366,10 @@
         <v>226.62</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>198.48</v>
+        <v>199.67</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>259.94</v>
+        <v>261.5</v>
       </c>
       <c r="F231" s="7" t="inlineStr"/>
     </row>
@@ -5386,10 +5386,10 @@
         <v>137.68</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>168.56</v>
+        <v>169.57</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>156.97</v>
+        <v>157.92</v>
       </c>
       <c r="F232" s="7" t="inlineStr"/>
     </row>
@@ -5406,10 +5406,10 @@
         <v>68.95</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>105.94</v>
+        <v>106.57</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>78.13</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F233" s="7" t="inlineStr"/>
     </row>
@@ -5426,10 +5426,10 @@
         <v>55.1</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>70.40000000000001</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>62.06</v>
+        <v>62.43</v>
       </c>
       <c r="F234" s="7" t="inlineStr"/>
     </row>
@@ -5446,10 +5446,10 @@
         <v>14.86</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>39.66</v>
+        <v>39.9</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>16.63</v>
+        <v>16.73</v>
       </c>
       <c r="F235" s="7" t="inlineStr"/>
     </row>
@@ -5466,10 +5466,10 @@
         <v>41.16</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>63.74</v>
+        <v>64.13</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>45.87</v>
+        <v>46.14</v>
       </c>
       <c r="F236" s="7" t="inlineStr"/>
     </row>
@@ -5486,10 +5486,10 @@
         <v>130.19</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>107.67</v>
+        <v>108.31</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>144.43</v>
+        <v>145.3</v>
       </c>
       <c r="F237" s="7" t="inlineStr"/>
     </row>
@@ -5506,10 +5506,10 @@
         <v>54.46</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>71.7</v>
+        <v>72.13</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>60.15</v>
+        <v>60.51</v>
       </c>
       <c r="F238" s="7" t="inlineStr"/>
     </row>
@@ -5526,10 +5526,10 @@
         <v>81.17</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>93.63</v>
+        <v>94.2</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>89.39</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="F239" s="7" t="inlineStr"/>
     </row>
@@ -5546,10 +5546,10 @@
         <v>236.79</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>217.76</v>
+        <v>219.07</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>260.04</v>
+        <v>261.6</v>
       </c>
       <c r="F240" s="7" t="inlineStr"/>
     </row>
@@ -5566,10 +5566,10 @@
         <v>125.95</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>93.73</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>137.93</v>
+        <v>138.75</v>
       </c>
       <c r="F241" s="7" t="inlineStr"/>
     </row>
@@ -5586,10 +5586,10 @@
         <v>94.95999999999999</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>79.37</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>103.59</v>
+        <v>104.21</v>
       </c>
       <c r="F242" s="7" t="inlineStr"/>
     </row>
@@ -5606,10 +5606,10 @@
         <v>216.23</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>174.16</v>
+        <v>175.2</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>234.98</v>
+        <v>236.39</v>
       </c>
       <c r="F243" s="7" t="inlineStr"/>
     </row>
@@ -5626,10 +5626,10 @@
         <v>34.35</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>44.73</v>
+        <v>45</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>37.19</v>
+        <v>37.41</v>
       </c>
       <c r="F244" s="7" t="inlineStr"/>
     </row>
@@ -5646,10 +5646,10 @@
         <v>9.57</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>16.33</v>
+        <v>16.43</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>10.34</v>
+        <v>10.4</v>
       </c>
       <c r="F245" s="7" t="inlineStr"/>
     </row>
@@ -5666,10 +5666,10 @@
         <v>48.53</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>48.43</v>
+        <v>48.72</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>52.32</v>
+        <v>52.63</v>
       </c>
       <c r="F246" s="7" t="inlineStr"/>
     </row>
@@ -5686,10 +5686,10 @@
         <v>45.54</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>40.91</v>
+        <v>41.16</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>48.99</v>
+        <v>49.29</v>
       </c>
       <c r="F247" s="7" t="inlineStr"/>
     </row>
@@ -5706,10 +5706,10 @@
         <v>23.49</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>35.11</v>
+        <v>35.32</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>25.19</v>
+        <v>25.34</v>
       </c>
       <c r="F248" s="7" t="inlineStr"/>
     </row>
@@ -5726,10 +5726,10 @@
         <v>74.73999999999999</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>70.64</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>79.91</v>
+        <v>80.39</v>
       </c>
       <c r="F249" s="7" t="inlineStr"/>
     </row>
@@ -5746,10 +5746,10 @@
         <v>70.23999999999999</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>71.56</v>
+        <v>71.98</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>74.87</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="F250" s="7" t="inlineStr"/>
     </row>
@@ -5766,10 +5766,10 @@
         <v>81.98999999999999</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>98.25</v>
+        <v>98.84</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>87.09</v>
+        <v>87.61</v>
       </c>
       <c r="F251" s="7" t="inlineStr"/>
     </row>
@@ -5786,10 +5786,10 @@
         <v>143.45</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>143.65</v>
+        <v>144.51</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>151.85</v>
+        <v>152.76</v>
       </c>
       <c r="F252" s="7" t="inlineStr"/>
     </row>
@@ -5806,10 +5806,10 @@
         <v>212.87</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>186.37</v>
+        <v>187.49</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>224.55</v>
+        <v>225.9</v>
       </c>
       <c r="F253" s="7" t="inlineStr"/>
     </row>
@@ -5826,10 +5826,10 @@
         <v>295.38</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>254.27</v>
+        <v>255.8</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>311.36</v>
+        <v>313.23</v>
       </c>
       <c r="F254" s="7" t="inlineStr"/>
     </row>
@@ -5846,10 +5846,10 @@
         <v>219.7</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>157.5</v>
+        <v>158.44</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>231.42</v>
+        <v>232.81</v>
       </c>
       <c r="F255" s="7" t="inlineStr"/>
     </row>
@@ -5866,10 +5866,10 @@
         <v>144.76</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>84.51000000000001</v>
+        <v>85.02</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>152.37</v>
+        <v>153.28</v>
       </c>
       <c r="F256" s="7" t="inlineStr"/>
     </row>
@@ -5886,10 +5886,10 @@
         <v>29.04</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>37.07</v>
+        <v>37.29</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>30.55</v>
+        <v>30.73</v>
       </c>
       <c r="F257" s="7" t="inlineStr"/>
     </row>
@@ -5906,10 +5906,10 @@
         <v>49.02</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>64.03</v>
+        <v>64.41</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>51.53</v>
+        <v>51.84</v>
       </c>
       <c r="F258" s="7" t="inlineStr"/>
     </row>
@@ -5926,10 +5926,10 @@
         <v>47.42</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>64.56999999999999</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>49.82</v>
+        <v>50.11</v>
       </c>
       <c r="F259" s="7" t="inlineStr"/>
     </row>
@@ -5946,10 +5946,10 @@
         <v>8.76</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>9.17</v>
+        <v>9.23</v>
       </c>
       <c r="F260" s="7" t="inlineStr"/>
     </row>
@@ -5966,10 +5966,10 @@
         <v>87.75</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>95.37</v>
+        <v>95.94</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>91.62</v>
+        <v>92.17</v>
       </c>
       <c r="F261" s="7" t="inlineStr"/>
     </row>
@@ -5986,10 +5986,10 @@
         <v>55.45</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>64.31999999999999</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>57.72</v>
+        <v>58.07</v>
       </c>
       <c r="F262" s="7" t="inlineStr"/>
     </row>
@@ -6006,10 +6006,10 @@
         <v>82.23</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>92.23</v>
+        <v>92.78</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>85.38</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F263" s="7" t="inlineStr"/>
     </row>
@@ -6026,10 +6026,10 @@
         <v>93.44</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>86.29000000000001</v>
+        <v>86.81</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>96.78</v>
+        <v>97.36</v>
       </c>
       <c r="F264" s="7" t="inlineStr"/>
     </row>
@@ -6046,10 +6046,10 @@
         <v>424.64</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>258.72</v>
+        <v>260.27</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>438.75</v>
+        <v>441.38</v>
       </c>
       <c r="F265" s="7" t="inlineStr"/>
     </row>
@@ -6066,10 +6066,10 @@
         <v>223.67</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>169.68</v>
+        <v>170.7</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>230.09</v>
+        <v>231.47</v>
       </c>
       <c r="F266" s="7" t="inlineStr"/>
     </row>
@@ -6086,10 +6086,10 @@
         <v>84.67</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>88.95999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>86.72</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="F267" s="7" t="inlineStr"/>
     </row>
@@ -6106,10 +6106,10 @@
         <v>57.7</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>58.74</v>
+        <v>59.09</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>58.84</v>
+        <v>59.19</v>
       </c>
       <c r="F268" s="7" t="inlineStr"/>
     </row>
@@ -6126,10 +6126,10 @@
         <v>40.14</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>51.06</v>
+        <v>51.37</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>40.85</v>
+        <v>41.1</v>
       </c>
       <c r="F269" s="7" t="inlineStr"/>
     </row>
@@ -6146,10 +6146,10 @@
         <v>9.94</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>32.99</v>
+        <v>33.19</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
       <c r="F270" s="7" t="inlineStr"/>
     </row>
@@ -6166,7 +6166,7 @@
         <v>-0.41</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>28.3</v>
+        <v>28.47</v>
       </c>
       <c r="E271" s="5" t="n">
         <v>-0.42</v>
@@ -6186,10 +6186,10 @@
         <v>250.71</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>153.64</v>
+        <v>154.56</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>253</v>
+        <v>254.52</v>
       </c>
       <c r="F272" s="7" t="inlineStr"/>
     </row>
@@ -6206,10 +6206,10 @@
         <v>34.52</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>56.25</v>
+        <v>56.59</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>34.68</v>
+        <v>34.88</v>
       </c>
       <c r="F273" s="7" t="inlineStr"/>
     </row>
@@ -6226,10 +6226,10 @@
         <v>35.84</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>43.95</v>
+        <v>44.21</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>35.84</v>
+        <v>36.05</v>
       </c>
       <c r="F274" s="7" t="inlineStr"/>
     </row>
@@ -6246,10 +6246,10 @@
         <v>58.97</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>54.93</v>
+        <v>55.15</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>58.97</v>
+        <v>59.21</v>
       </c>
       <c r="F275" s="7" t="inlineStr"/>
     </row>
@@ -6266,10 +6266,10 @@
         <v>59.52</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>55.79</v>
+        <v>55.9</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>59.52</v>
+        <v>59.64</v>
       </c>
       <c r="F276" s="7" t="inlineStr"/>
     </row>
@@ -6312,6 +6312,26 @@
         <v>108.02</v>
       </c>
       <c r="F278" s="7" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="F279" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6324,7 +6344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E278"/>
+  <dimension ref="A1:E279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6374,10 +6394,10 @@
         <v>34.07</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>50.33</v>
+        <v>50.63</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>63.32</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="3">
@@ -6393,10 +6413,10 @@
         <v>26.44</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>42.29</v>
+        <v>42.55</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>49.04</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="4">
@@ -6412,10 +6432,10 @@
         <v>27.77</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>43.05</v>
+        <v>43.3</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>51.41</v>
+        <v>51.72</v>
       </c>
     </row>
     <row r="5">
@@ -6431,10 +6451,10 @@
         <v>29.25</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>46.45</v>
+        <v>46.72</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>54.06</v>
+        <v>54.38</v>
       </c>
     </row>
     <row r="6">
@@ -6450,10 +6470,10 @@
         <v>50.3</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>59.98</v>
+        <v>60.34</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>92.8</v>
+        <v>93.36</v>
       </c>
     </row>
     <row r="7">
@@ -6469,10 +6489,10 @@
         <v>43.98</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>56.65</v>
+        <v>56.99</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>81</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="8">
@@ -6488,10 +6508,10 @@
         <v>37.22</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>60.12</v>
+        <v>60.48</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>68.34999999999999</v>
+        <v>68.76000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -6507,10 +6527,10 @@
         <v>108.46</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>158.98</v>
+        <v>159.93</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>198.58</v>
+        <v>199.77</v>
       </c>
     </row>
     <row r="10">
@@ -6526,10 +6546,10 @@
         <v>64.37</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>76.22</v>
+        <v>76.67</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>117.51</v>
+        <v>118.21</v>
       </c>
     </row>
     <row r="11">
@@ -6545,10 +6565,10 @@
         <v>37.5</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>57.49</v>
+        <v>57.83</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>68.34999999999999</v>
+        <v>68.76000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -6564,10 +6584,10 @@
         <v>40.38</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>62.02</v>
+        <v>62.39</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>73.48999999999999</v>
+        <v>73.93000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -6583,10 +6603,10 @@
         <v>36.85</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>59.18</v>
+        <v>59.54</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>66.95999999999999</v>
+        <v>67.36</v>
       </c>
     </row>
     <row r="14">
@@ -6602,10 +6622,10 @@
         <v>50.28</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>71.64</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>91.23999999999999</v>
+        <v>91.78</v>
       </c>
     </row>
     <row r="15">
@@ -6621,10 +6641,10 @@
         <v>33.56</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>58.66</v>
+        <v>59.01</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>60.81</v>
+        <v>61.18</v>
       </c>
     </row>
     <row r="16">
@@ -6640,10 +6660,10 @@
         <v>34.17</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>55.59</v>
+        <v>55.92</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>61.83</v>
+        <v>62.21</v>
       </c>
     </row>
     <row r="17">
@@ -6659,10 +6679,10 @@
         <v>54.24</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>74.45999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>97.90000000000001</v>
+        <v>98.48999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -6678,10 +6698,10 @@
         <v>94.34999999999999</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>116.83</v>
+        <v>117.53</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>169.87</v>
+        <v>170.89</v>
       </c>
     </row>
     <row r="19">
@@ -6697,10 +6717,10 @@
         <v>40.24</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>60.65</v>
+        <v>61.01</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>72.27</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="20">
@@ -6716,10 +6736,10 @@
         <v>41.25</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>55.14</v>
+        <v>55.47</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>73.91</v>
+        <v>74.36</v>
       </c>
     </row>
     <row r="21">
@@ -6735,10 +6755,10 @@
         <v>32.11</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>46.48</v>
+        <v>46.76</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>57.41</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="22">
@@ -6754,10 +6774,10 @@
         <v>43.91</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>56.85</v>
+        <v>57.19</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>78.33</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="23">
@@ -6773,10 +6793,10 @@
         <v>42.74</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>62.9</v>
+        <v>63.28</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>76.09</v>
+        <v>76.55</v>
       </c>
     </row>
     <row r="24">
@@ -6792,10 +6812,10 @@
         <v>46.01</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>67.34</v>
+        <v>67.75</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>81.75</v>
+        <v>82.23999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -6811,10 +6831,10 @@
         <v>32.96</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>49.56</v>
+        <v>49.86</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>58.45</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="26">
@@ -6830,10 +6850,10 @@
         <v>37.36</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>54.42</v>
+        <v>54.75</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>66.03</v>
+        <v>66.43000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -6849,10 +6869,10 @@
         <v>43.61</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>58.45</v>
+        <v>58.8</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>76.83</v>
+        <v>77.29000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -6868,10 +6888,10 @@
         <v>38.81</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>55.03</v>
+        <v>55.36</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>68.15000000000001</v>
+        <v>68.55</v>
       </c>
     </row>
     <row r="29">
@@ -6887,10 +6907,10 @@
         <v>37.79</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>52.85</v>
+        <v>53.17</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>66.23999999999999</v>
+        <v>66.64</v>
       </c>
     </row>
     <row r="30">
@@ -6906,10 +6926,10 @@
         <v>64.09</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>71.08</v>
+        <v>71.5</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>112.15</v>
+        <v>112.82</v>
       </c>
     </row>
     <row r="31">
@@ -6925,10 +6945,10 @@
         <v>71.84999999999999</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>81.38</v>
+        <v>81.87</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>125.51</v>
+        <v>126.26</v>
       </c>
     </row>
     <row r="32">
@@ -6944,10 +6964,10 @@
         <v>109.21</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>126.65</v>
+        <v>127.41</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>190.23</v>
+        <v>191.37</v>
       </c>
     </row>
     <row r="33">
@@ -6963,10 +6983,10 @@
         <v>48.02</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>54.68</v>
+        <v>55</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>83.40000000000001</v>
+        <v>83.91</v>
       </c>
     </row>
     <row r="34">
@@ -6982,10 +7002,10 @@
         <v>36.24</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>51.27</v>
+        <v>51.57</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>62.77</v>
+        <v>63.14</v>
       </c>
     </row>
     <row r="35">
@@ -7001,10 +7021,10 @@
         <v>33.95</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>48.05</v>
+        <v>48.34</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>58.49</v>
+        <v>58.84</v>
       </c>
     </row>
     <row r="36">
@@ -7020,10 +7040,10 @@
         <v>52.72</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>66.09</v>
+        <v>66.48</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>90.34999999999999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -7039,10 +7059,10 @@
         <v>47.94</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>66.87</v>
+        <v>67.27</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>81.73999999999999</v>
+        <v>82.23</v>
       </c>
     </row>
     <row r="38">
@@ -7058,10 +7078,10 @@
         <v>70.05</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>84.73999999999999</v>
+        <v>85.25</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>119.08</v>
+        <v>119.79</v>
       </c>
     </row>
     <row r="39">
@@ -7077,10 +7097,10 @@
         <v>42.93</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>63.81</v>
+        <v>64.2</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>72.76000000000001</v>
+        <v>73.2</v>
       </c>
     </row>
     <row r="40">
@@ -7096,10 +7116,10 @@
         <v>38.55</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>53.45</v>
+        <v>53.77</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>65.15000000000001</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -7115,10 +7135,10 @@
         <v>36.13</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>49.38</v>
+        <v>49.68</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>61.08</v>
+        <v>61.45</v>
       </c>
     </row>
     <row r="42">
@@ -7134,10 +7154,10 @@
         <v>44.26</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>61.48</v>
+        <v>61.85</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>74.84999999999999</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="43">
@@ -7153,10 +7173,10 @@
         <v>57.46</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>65.45999999999999</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>97.22</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="44">
@@ -7172,10 +7192,10 @@
         <v>111.81</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>112.46</v>
+        <v>113.14</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>189.12</v>
+        <v>190.25</v>
       </c>
     </row>
     <row r="45">
@@ -7191,10 +7211,10 @@
         <v>75.23999999999999</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>89.23</v>
+        <v>89.77</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>127.23</v>
+        <v>127.99</v>
       </c>
     </row>
     <row r="46">
@@ -7210,10 +7230,10 @@
         <v>69.39</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>82.11</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>117.3</v>
+        <v>118.01</v>
       </c>
     </row>
     <row r="47">
@@ -7229,10 +7249,10 @@
         <v>82.88</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>117.5</v>
+        <v>118.2</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>139.54</v>
+        <v>140.37</v>
       </c>
     </row>
     <row r="48">
@@ -7248,10 +7268,10 @@
         <v>70.90000000000001</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>95.47</v>
+        <v>96.05</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>118.88</v>
+        <v>119.59</v>
       </c>
     </row>
     <row r="49">
@@ -7267,10 +7287,10 @@
         <v>133.72</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>171.39</v>
+        <v>172.42</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>223.31</v>
+        <v>224.65</v>
       </c>
     </row>
     <row r="50">
@@ -7286,10 +7306,10 @@
         <v>113.89</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>142.6</v>
+        <v>143.46</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>189.75</v>
+        <v>190.89</v>
       </c>
     </row>
     <row r="51">
@@ -7305,10 +7325,10 @@
         <v>50.5</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>69.15000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>83.95</v>
+        <v>84.45</v>
       </c>
     </row>
     <row r="52">
@@ -7324,10 +7344,10 @@
         <v>53.16</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>71.55</v>
+        <v>71.98</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>88.17</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="53">
@@ -7343,10 +7363,10 @@
         <v>43.35</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>58.12</v>
+        <v>58.47</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>71.67</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -7362,10 +7382,10 @@
         <v>54.39</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>69.29000000000001</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>89.65000000000001</v>
+        <v>90.19</v>
       </c>
     </row>
     <row r="55">
@@ -7381,10 +7401,10 @@
         <v>63.76</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>75.13</v>
+        <v>75.58</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>104.77</v>
+        <v>105.4</v>
       </c>
     </row>
     <row r="56">
@@ -7400,10 +7420,10 @@
         <v>226.68</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>197.03</v>
+        <v>198.21</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>370.83</v>
+        <v>373.06</v>
       </c>
     </row>
     <row r="57">
@@ -7419,10 +7439,10 @@
         <v>248.69</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>206.19</v>
+        <v>207.43</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>405.04</v>
+        <v>407.47</v>
       </c>
     </row>
     <row r="58">
@@ -7438,10 +7458,10 @@
         <v>450.11</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>337.53</v>
+        <v>339.55</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>729.85</v>
+        <v>734.23</v>
       </c>
     </row>
     <row r="59">
@@ -7457,10 +7477,10 @@
         <v>51.23</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>67.42</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>82.67</v>
+        <v>83.17</v>
       </c>
     </row>
     <row r="60">
@@ -7476,10 +7496,10 @@
         <v>60.14</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>96.58</v>
+        <v>97.16</v>
       </c>
     </row>
     <row r="61">
@@ -7495,10 +7515,10 @@
         <v>48.05</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>64.11</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>76.8</v>
+        <v>77.26000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -7514,10 +7534,10 @@
         <v>60.06</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>69.23</v>
+        <v>69.64</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>95.62</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="63">
@@ -7533,10 +7553,10 @@
         <v>50.93</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>65.42</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>80.78</v>
+        <v>81.26000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -7552,10 +7572,10 @@
         <v>40.83</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>49.82</v>
+        <v>50.11</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>64.51000000000001</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -7571,10 +7591,10 @@
         <v>45.57</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>56.26</v>
+        <v>56.6</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>72.08</v>
+        <v>72.51000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -7590,10 +7610,10 @@
         <v>43.01</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>50.73</v>
+        <v>51.04</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>68.09999999999999</v>
+        <v>68.51000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -7609,10 +7629,10 @@
         <v>29.77</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>38.88</v>
+        <v>39.12</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>47.19</v>
+        <v>47.47</v>
       </c>
     </row>
     <row r="68">
@@ -7628,10 +7648,10 @@
         <v>475</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>362.3</v>
+        <v>364.47</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>752.65</v>
+        <v>757.16</v>
       </c>
     </row>
     <row r="69">
@@ -7647,10 +7667,10 @@
         <v>51.77</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>61.2</v>
+        <v>61.57</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>82</v>
+        <v>82.48999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -7666,10 +7686,10 @@
         <v>45.09</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>50.32</v>
+        <v>50.62</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>71.39</v>
+        <v>71.81999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -7685,10 +7705,10 @@
         <v>45.7</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>56.23</v>
+        <v>56.56</v>
       </c>
       <c r="E71" s="5" t="n">
-        <v>72.23999999999999</v>
+        <v>72.67</v>
       </c>
     </row>
     <row r="72">
@@ -7704,10 +7724,10 @@
         <v>39.59</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>53.36</v>
+        <v>53.68</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>62.48</v>
+        <v>62.85</v>
       </c>
     </row>
     <row r="73">
@@ -7723,10 +7743,10 @@
         <v>38.18</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>49.3</v>
+        <v>49.59</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>60.15</v>
+        <v>60.51</v>
       </c>
     </row>
     <row r="74">
@@ -7742,10 +7762,10 @@
         <v>33.22</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>42.97</v>
+        <v>43.23</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>52.17</v>
+        <v>52.49</v>
       </c>
     </row>
     <row r="75">
@@ -7761,10 +7781,10 @@
         <v>29.21</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>35.63</v>
+        <v>35.85</v>
       </c>
       <c r="E75" s="5" t="n">
-        <v>45.73</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="76">
@@ -7780,10 +7800,10 @@
         <v>33.51</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>40.95</v>
+        <v>41.2</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>52.3</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="77">
@@ -7799,10 +7819,10 @@
         <v>35.31</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>43.59</v>
+        <v>43.85</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>55.01</v>
+        <v>55.34</v>
       </c>
     </row>
     <row r="78">
@@ -7818,10 +7838,10 @@
         <v>418.99</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>306.7</v>
+        <v>308.54</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>651.62</v>
+        <v>655.52</v>
       </c>
     </row>
     <row r="79">
@@ -7837,10 +7857,10 @@
         <v>29.75</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>36.99</v>
+        <v>37.22</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>46.18</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="80">
@@ -7856,10 +7876,10 @@
         <v>190.57</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>150.69</v>
+        <v>151.6</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>294.93</v>
+        <v>296.7</v>
       </c>
     </row>
     <row r="81">
@@ -7875,10 +7895,10 @@
         <v>267.21</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>203.72</v>
+        <v>204.94</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>412.27</v>
+        <v>414.74</v>
       </c>
     </row>
     <row r="82">
@@ -7894,10 +7914,10 @@
         <v>27.63</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>36.27</v>
+        <v>36.49</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>42.5</v>
+        <v>42.75</v>
       </c>
     </row>
     <row r="83">
@@ -7913,10 +7933,10 @@
         <v>36.87</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>45.38</v>
+        <v>45.65</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>56.6</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="84">
@@ -7932,10 +7952,10 @@
         <v>34.27</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>45.93</v>
+        <v>46.2</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>52.5</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="85">
@@ -7951,10 +7971,10 @@
         <v>40.33</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>54.17</v>
+        <v>54.49</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>61.66</v>
+        <v>62.03</v>
       </c>
     </row>
     <row r="86">
@@ -7970,10 +7990,10 @@
         <v>32.6</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>44.66</v>
+        <v>44.93</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>49.72</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="87">
@@ -7989,10 +8009,10 @@
         <v>31.21</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>39.51</v>
+        <v>39.75</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>47.49</v>
+        <v>47.77</v>
       </c>
     </row>
     <row r="88">
@@ -8008,10 +8028,10 @@
         <v>31.03</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>38.07</v>
+        <v>38.3</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>47.1</v>
+        <v>47.38</v>
       </c>
     </row>
     <row r="89">
@@ -8027,10 +8047,10 @@
         <v>35.53</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>33.68</v>
+        <v>33.89</v>
       </c>
       <c r="E89" s="5" t="n">
-        <v>53.86</v>
+        <v>54.18</v>
       </c>
     </row>
     <row r="90">
@@ -8046,10 +8066,10 @@
         <v>30.93</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>34.17</v>
+        <v>34.38</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>46.83</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="91">
@@ -8065,10 +8085,10 @@
         <v>21.64</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>26.6</v>
+        <v>26.76</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>32.72</v>
+        <v>32.92</v>
       </c>
     </row>
     <row r="92">
@@ -8084,10 +8104,10 @@
         <v>208.38</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>155.12</v>
+        <v>156.05</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>313.46</v>
+        <v>315.34</v>
       </c>
     </row>
     <row r="93">
@@ -8103,10 +8123,10 @@
         <v>38.34</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>44.87</v>
+        <v>45.14</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>57.38</v>
+        <v>57.72</v>
       </c>
     </row>
     <row r="94">
@@ -8122,10 +8142,10 @@
         <v>27.5</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>33.31</v>
+        <v>33.51</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>40.95</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="95">
@@ -8141,10 +8161,10 @@
         <v>29.82</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>40.48</v>
+        <v>40.72</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>44.27</v>
+        <v>44.53</v>
       </c>
     </row>
     <row r="96">
@@ -8160,10 +8180,10 @@
         <v>38.76</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>49.71</v>
+        <v>50.01</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>57.36</v>
+        <v>57.71</v>
       </c>
     </row>
     <row r="97">
@@ -8179,10 +8199,10 @@
         <v>37.31</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>45.49</v>
+        <v>45.76</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>55.05</v>
+        <v>55.38</v>
       </c>
     </row>
     <row r="98">
@@ -8198,10 +8218,10 @@
         <v>42.39</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>48.77</v>
+        <v>49.06</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>62.42</v>
+        <v>62.79</v>
       </c>
     </row>
     <row r="99">
@@ -8217,10 +8237,10 @@
         <v>38.44</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>50.64</v>
+        <v>50.95</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>56.49</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="100">
@@ -8236,10 +8256,10 @@
         <v>44.12</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>55.69</v>
+        <v>56.02</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>64.70999999999999</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -8255,10 +8275,10 @@
         <v>52.46</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>59.09</v>
+        <v>59.45</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>76.94</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -8274,10 +8294,10 @@
         <v>35.82</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>45</v>
+        <v>45.27</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>52.54</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="103">
@@ -8293,10 +8313,10 @@
         <v>27.64</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>34.86</v>
+        <v>35.07</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>40.54</v>
+        <v>40.78</v>
       </c>
     </row>
     <row r="104">
@@ -8312,10 +8332,10 @@
         <v>31.12</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>37.57</v>
+        <v>37.79</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>45.63</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="105">
@@ -8331,10 +8351,10 @@
         <v>31.06</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>39.81</v>
+        <v>40.04</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>45.54</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="106">
@@ -8350,10 +8370,10 @@
         <v>29.6</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>37.73</v>
+        <v>37.96</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>43.39</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="107">
@@ -8369,10 +8389,10 @@
         <v>29.99</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>42.6</v>
+        <v>42.85</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>43.88</v>
+        <v>44.15</v>
       </c>
     </row>
     <row r="108">
@@ -8388,10 +8408,10 @@
         <v>32.16</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>42.51</v>
+        <v>42.76</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>46.98</v>
+        <v>47.26</v>
       </c>
     </row>
     <row r="109">
@@ -8407,10 +8427,10 @@
         <v>42.59</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>38.19</v>
+        <v>38.42</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>62.11</v>
+        <v>62.48</v>
       </c>
     </row>
     <row r="110">
@@ -8426,10 +8446,10 @@
         <v>97.23</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>115.74</v>
+        <v>116.44</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>141.15</v>
+        <v>141.99</v>
       </c>
     </row>
     <row r="111">
@@ -8445,10 +8465,10 @@
         <v>65.08</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>91.51000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>94.05</v>
+        <v>94.61</v>
       </c>
     </row>
     <row r="112">
@@ -8464,10 +8484,10 @@
         <v>61.09</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.87</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>87.89</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="113">
@@ -8483,10 +8503,10 @@
         <v>55.05</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>73.25</v>
+        <v>73.69</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>79.13</v>
+        <v>79.61</v>
       </c>
     </row>
     <row r="114">
@@ -8502,10 +8522,10 @@
         <v>78.5</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>93.7</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>112.74</v>
+        <v>113.42</v>
       </c>
     </row>
     <row r="115">
@@ -8521,10 +8541,10 @@
         <v>60.95</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>76.64</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>87.45999999999999</v>
+        <v>87.98999999999999</v>
       </c>
     </row>
     <row r="116">
@@ -8540,10 +8560,10 @@
         <v>74.05</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>84.73999999999999</v>
+        <v>85.25</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>106.14</v>
+        <v>106.78</v>
       </c>
     </row>
     <row r="117">
@@ -8559,10 +8579,10 @@
         <v>63.97</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>83.8</v>
+        <v>84.31</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>91.59</v>
+        <v>92.14</v>
       </c>
     </row>
     <row r="118">
@@ -8578,10 +8598,10 @@
         <v>67.98</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>82.45999999999999</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>97.22</v>
+        <v>97.81</v>
       </c>
     </row>
     <row r="119">
@@ -8597,10 +8617,10 @@
         <v>92.58</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>109.83</v>
+        <v>110.49</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>132.24</v>
+        <v>133.03</v>
       </c>
     </row>
     <row r="120">
@@ -8616,10 +8636,10 @@
         <v>137.04</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>155.14</v>
+        <v>156.07</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>195.5</v>
+        <v>196.67</v>
       </c>
     </row>
     <row r="121">
@@ -8635,10 +8655,10 @@
         <v>161.64</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>155.74</v>
+        <v>156.68</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>230.3</v>
+        <v>231.68</v>
       </c>
     </row>
     <row r="122">
@@ -8654,10 +8674,10 @@
         <v>80.34999999999999</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>98.83</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>114.02</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="123">
@@ -8673,10 +8693,10 @@
         <v>82.62</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>100.68</v>
+        <v>101.29</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>116.77</v>
+        <v>117.47</v>
       </c>
     </row>
     <row r="124">
@@ -8692,10 +8712,10 @@
         <v>73.02</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>86.29000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>102.78</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="125">
@@ -8711,10 +8731,10 @@
         <v>64.76000000000001</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>80.67</v>
+        <v>81.16</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>90.94</v>
+        <v>91.48</v>
       </c>
     </row>
     <row r="126">
@@ -8730,10 +8750,10 @@
         <v>54.57</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>69.78</v>
+        <v>70.2</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>76.45</v>
+        <v>76.91</v>
       </c>
     </row>
     <row r="127">
@@ -8749,10 +8769,10 @@
         <v>119</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>111.2</v>
+        <v>111.87</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>166.31</v>
+        <v>167.31</v>
       </c>
     </row>
     <row r="128">
@@ -8768,10 +8788,10 @@
         <v>137.47</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>123.96</v>
+        <v>124.7</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>191.74</v>
+        <v>192.89</v>
       </c>
     </row>
     <row r="129">
@@ -8787,10 +8807,10 @@
         <v>59.75</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>80.02</v>
+        <v>80.5</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>83.18000000000001</v>
+        <v>83.68000000000001</v>
       </c>
     </row>
     <row r="130">
@@ -8806,10 +8826,10 @@
         <v>55.71</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>68.31</v>
+        <v>68.72</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="131">
@@ -8825,10 +8845,10 @@
         <v>51.23</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>66.77</v>
+        <v>67.17</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>71.06</v>
+        <v>71.48</v>
       </c>
     </row>
     <row r="132">
@@ -8844,10 +8864,10 @@
         <v>58.5</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>71.98</v>
+        <v>72.41</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>81</v>
+        <v>81.48999999999999</v>
       </c>
     </row>
     <row r="133">
@@ -8863,10 +8883,10 @@
         <v>59.79</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>75.23</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>82.65000000000001</v>
+        <v>83.15000000000001</v>
       </c>
     </row>
     <row r="134">
@@ -8882,10 +8902,10 @@
         <v>60.81</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>71.45</v>
+        <v>71.88</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>83.94</v>
+        <v>84.45</v>
       </c>
     </row>
     <row r="135">
@@ -8901,10 +8921,10 @@
         <v>50.71</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>57.43</v>
+        <v>57.77</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>70.31999999999999</v>
       </c>
     </row>
     <row r="136">
@@ -8920,10 +8940,10 @@
         <v>49.36</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>56.52</v>
+        <v>56.86</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>67.95</v>
+        <v>68.34999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -8939,10 +8959,10 @@
         <v>34.86</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>44.05</v>
+        <v>44.31</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>47.96</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="138">
@@ -8958,10 +8978,10 @@
         <v>35.52</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>44.98</v>
+        <v>45.25</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>48.83</v>
+        <v>49.13</v>
       </c>
     </row>
     <row r="139">
@@ -8977,10 +8997,10 @@
         <v>31.78</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>39.35</v>
+        <v>39.59</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>43.66</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="140">
@@ -8996,10 +9016,10 @@
         <v>47.98</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>47.62</v>
+        <v>47.9</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>65.88</v>
+        <v>66.28</v>
       </c>
     </row>
     <row r="141">
@@ -9015,10 +9035,10 @@
         <v>49.24</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>61.54</v>
+        <v>61.91</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>67.56999999999999</v>
+        <v>67.97</v>
       </c>
     </row>
     <row r="142">
@@ -9034,10 +9054,10 @@
         <v>34.48</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>39.14</v>
+        <v>39.37</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>47.28</v>
+        <v>47.57</v>
       </c>
     </row>
     <row r="143">
@@ -9053,10 +9073,10 @@
         <v>49.75</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>54.66</v>
+        <v>54.98</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>68.06</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="144">
@@ -9072,10 +9092,10 @@
         <v>43.01</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>51.89</v>
+        <v>52.2</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>58.7</v>
+        <v>59.05</v>
       </c>
     </row>
     <row r="145">
@@ -9091,10 +9111,10 @@
         <v>87.84</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>79.81</v>
+        <v>80.28</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>119.61</v>
+        <v>120.32</v>
       </c>
     </row>
     <row r="146">
@@ -9110,10 +9130,10 @@
         <v>105.03</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>99.95999999999999</v>
+        <v>100.56</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>142.83</v>
+        <v>143.68</v>
       </c>
     </row>
     <row r="147">
@@ -9129,10 +9149,10 @@
         <v>64.77</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>82.44</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>87.95999999999999</v>
+        <v>88.48999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -9148,10 +9168,10 @@
         <v>72.77</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>80.12</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>98.7</v>
+        <v>99.29000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -9167,10 +9187,10 @@
         <v>51.88</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>55.67</v>
+        <v>56.01</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>70.28</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="150">
@@ -9186,10 +9206,10 @@
         <v>63.99</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>66.13</v>
+        <v>66.53</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>86.56999999999999</v>
+        <v>87.09</v>
       </c>
     </row>
     <row r="151">
@@ -9205,10 +9225,10 @@
         <v>97.42</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>90.3</v>
+        <v>90.84</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>131.63</v>
+        <v>132.42</v>
       </c>
     </row>
     <row r="152">
@@ -9224,10 +9244,10 @@
         <v>71.81</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>67.95</v>
+        <v>68.36</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>97.09</v>
+        <v>97.67</v>
       </c>
     </row>
     <row r="153">
@@ -9243,10 +9263,10 @@
         <v>53.34</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>55.09</v>
+        <v>55.42</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>72.17</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -9262,10 +9282,10 @@
         <v>73.59</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>74.91</v>
+        <v>75.36</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>99.63</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="155">
@@ -9281,10 +9301,10 @@
         <v>63.34</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>67.01000000000001</v>
+        <v>67.41</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>85.63</v>
+        <v>86.14</v>
       </c>
     </row>
     <row r="156">
@@ -9300,10 +9320,10 @@
         <v>101.4</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>95.44</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>136.88</v>
+        <v>137.7</v>
       </c>
     </row>
     <row r="157">
@@ -9319,10 +9339,10 @@
         <v>162.44</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>165.93</v>
+        <v>166.92</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>218.95</v>
+        <v>220.27</v>
       </c>
     </row>
     <row r="158">
@@ -9338,10 +9358,10 @@
         <v>376.22</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>308.48</v>
+        <v>310.33</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>505.93</v>
+        <v>508.96</v>
       </c>
     </row>
     <row r="159">
@@ -9357,10 +9377,10 @@
         <v>86.52</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>88.87</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>116.08</v>
+        <v>116.77</v>
       </c>
     </row>
     <row r="160">
@@ -9376,10 +9396,10 @@
         <v>70.70999999999999</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>80.11</v>
+        <v>80.59</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>94.65000000000001</v>
+        <v>95.20999999999999</v>
       </c>
     </row>
     <row r="161">
@@ -9395,10 +9415,10 @@
         <v>71.86</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>79.18000000000001</v>
+        <v>79.66</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>96.02</v>
+        <v>96.59</v>
       </c>
     </row>
     <row r="162">
@@ -9414,10 +9434,10 @@
         <v>81.73999999999999</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>82.55</v>
+        <v>83.05</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>109.03</v>
+        <v>109.68</v>
       </c>
     </row>
     <row r="163">
@@ -9433,10 +9453,10 @@
         <v>92.59</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>129.55</v>
+        <v>130.33</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>123.28</v>
+        <v>124.02</v>
       </c>
     </row>
     <row r="164">
@@ -9452,10 +9472,10 @@
         <v>102.67</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>112.02</v>
+        <v>112.69</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>136.5</v>
+        <v>137.32</v>
       </c>
     </row>
     <row r="165">
@@ -9471,10 +9491,10 @@
         <v>298.82</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>238.74</v>
+        <v>240.17</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>396.67</v>
+        <v>399.05</v>
       </c>
     </row>
     <row r="166">
@@ -9490,10 +9510,10 @@
         <v>164.54</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>162.23</v>
+        <v>163.21</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>218.09</v>
+        <v>219.39</v>
       </c>
     </row>
     <row r="167">
@@ -9509,10 +9529,10 @@
         <v>140.44</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>158.54</v>
+        <v>159.49</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>186.02</v>
+        <v>187.14</v>
       </c>
     </row>
     <row r="168">
@@ -9528,10 +9548,10 @@
         <v>134.58</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>157.72</v>
+        <v>158.67</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>178.14</v>
+        <v>179.21</v>
       </c>
     </row>
     <row r="169">
@@ -9547,10 +9567,10 @@
         <v>113.03</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>143.96</v>
+        <v>144.83</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>149.52</v>
+        <v>150.42</v>
       </c>
     </row>
     <row r="170">
@@ -9566,10 +9586,10 @@
         <v>127.48</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>149.81</v>
+        <v>150.71</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>168.29</v>
+        <v>169.3</v>
       </c>
     </row>
     <row r="171">
@@ -9585,10 +9605,10 @@
         <v>126.76</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>138.84</v>
+        <v>139.67</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="172">
@@ -9604,10 +9624,10 @@
         <v>80.16</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>96.76000000000001</v>
+        <v>97.34</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>105.39</v>
+        <v>106.03</v>
       </c>
     </row>
     <row r="173">
@@ -9623,10 +9643,10 @@
         <v>76.89</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>90.98999999999999</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>100.87</v>
+        <v>101.47</v>
       </c>
     </row>
     <row r="174">
@@ -9642,10 +9662,10 @@
         <v>110.15</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>118.75</v>
+        <v>119.46</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>144.18</v>
+        <v>145.04</v>
       </c>
     </row>
     <row r="175">
@@ -9661,10 +9681,10 @@
         <v>93.62</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>109.07</v>
+        <v>109.72</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>122.27</v>
+        <v>123</v>
       </c>
     </row>
     <row r="176">
@@ -9680,10 +9700,10 @@
         <v>231.26</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>207.04</v>
+        <v>208.28</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>301.59</v>
+        <v>303.4</v>
       </c>
     </row>
     <row r="177">
@@ -9699,10 +9719,10 @@
         <v>143.22</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>142.16</v>
+        <v>143.02</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>186.51</v>
+        <v>187.62</v>
       </c>
     </row>
     <row r="178">
@@ -9718,10 +9738,10 @@
         <v>89.47</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>104.94</v>
+        <v>105.57</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>116.34</v>
+        <v>117.04</v>
       </c>
     </row>
     <row r="179">
@@ -9737,10 +9757,10 @@
         <v>134.3</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>127.76</v>
+        <v>128.53</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>174.43</v>
+        <v>175.47</v>
       </c>
     </row>
     <row r="180">
@@ -9756,10 +9776,10 @@
         <v>105.82</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>114.82</v>
+        <v>115.51</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>137.27</v>
+        <v>138.1</v>
       </c>
     </row>
     <row r="181">
@@ -9775,10 +9795,10 @@
         <v>125.64</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>137.24</v>
+        <v>138.06</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>162.79</v>
+        <v>163.77</v>
       </c>
     </row>
     <row r="182">
@@ -9794,10 +9814,10 @@
         <v>147.26</v>
       </c>
       <c r="D182" s="5" t="n">
-        <v>136.85</v>
+        <v>137.67</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>190.53</v>
+        <v>191.67</v>
       </c>
     </row>
     <row r="183">
@@ -9813,10 +9833,10 @@
         <v>89.47</v>
       </c>
       <c r="D183" s="5" t="n">
-        <v>93.42</v>
+        <v>93.98</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>115.59</v>
+        <v>116.29</v>
       </c>
     </row>
     <row r="184">
@@ -9832,10 +9852,10 @@
         <v>102.55</v>
       </c>
       <c r="D184" s="5" t="n">
-        <v>116.88</v>
+        <v>117.59</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>132.3</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="185">
@@ -9851,10 +9871,10 @@
         <v>105.22</v>
       </c>
       <c r="D185" s="5" t="n">
-        <v>126.37</v>
+        <v>127.13</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>135.51</v>
+        <v>136.32</v>
       </c>
     </row>
     <row r="186">
@@ -9870,10 +9890,10 @@
         <v>102.27</v>
       </c>
       <c r="D186" s="5" t="n">
-        <v>126.98</v>
+        <v>127.75</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>131.48</v>
+        <v>132.27</v>
       </c>
     </row>
     <row r="187">
@@ -9889,10 +9909,10 @@
         <v>111.5</v>
       </c>
       <c r="D187" s="5" t="n">
-        <v>118.56</v>
+        <v>119.28</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>143.1</v>
+        <v>143.96</v>
       </c>
     </row>
     <row r="188">
@@ -9908,10 +9928,10 @@
         <v>407.47</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>309.35</v>
+        <v>311.2</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>522.99</v>
+        <v>526.12</v>
       </c>
     </row>
     <row r="189">
@@ -9927,10 +9947,10 @@
         <v>117.28</v>
       </c>
       <c r="D189" s="5" t="n">
-        <v>142.13</v>
+        <v>142.98</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>150.53</v>
+        <v>151.44</v>
       </c>
     </row>
     <row r="190">
@@ -9946,10 +9966,10 @@
         <v>175.2</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>168.92</v>
+        <v>169.94</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>224.89</v>
+        <v>226.24</v>
       </c>
     </row>
     <row r="191">
@@ -9965,10 +9985,10 @@
         <v>97.14</v>
       </c>
       <c r="D191" s="5" t="n">
-        <v>120.22</v>
+        <v>120.94</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>124.44</v>
+        <v>125.19</v>
       </c>
     </row>
     <row r="192">
@@ -9984,10 +10004,10 @@
         <v>92.58</v>
       </c>
       <c r="D192" s="5" t="n">
-        <v>108.5</v>
+        <v>109.15</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>118.37</v>
+        <v>119.08</v>
       </c>
     </row>
     <row r="193">
@@ -10003,10 +10023,10 @@
         <v>113.86</v>
       </c>
       <c r="D193" s="5" t="n">
-        <v>122.12</v>
+        <v>122.85</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>145.29</v>
+        <v>146.16</v>
       </c>
     </row>
     <row r="194">
@@ -10022,10 +10042,10 @@
         <v>92.31999999999999</v>
       </c>
       <c r="D194" s="5" t="n">
-        <v>94.16</v>
+        <v>94.72</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>117.58</v>
+        <v>118.29</v>
       </c>
     </row>
     <row r="195">
@@ -10041,10 +10061,10 @@
         <v>99.59</v>
       </c>
       <c r="D195" s="5" t="n">
-        <v>100.15</v>
+        <v>100.75</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>126.6</v>
+        <v>127.36</v>
       </c>
     </row>
     <row r="196">
@@ -10060,10 +10080,10 @@
         <v>81.09999999999999</v>
       </c>
       <c r="D196" s="5" t="n">
-        <v>92.56</v>
+        <v>93.12</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>102.91</v>
+        <v>103.52</v>
       </c>
     </row>
     <row r="197">
@@ -10079,10 +10099,10 @@
         <v>69.06999999999999</v>
       </c>
       <c r="D197" s="5" t="n">
-        <v>85.25</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>87.44</v>
+        <v>87.97</v>
       </c>
     </row>
     <row r="198">
@@ -10098,10 +10118,10 @@
         <v>34.58</v>
       </c>
       <c r="D198" s="5" t="n">
-        <v>64.23999999999999</v>
+        <v>64.63</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>43.68</v>
+        <v>43.94</v>
       </c>
     </row>
     <row r="199">
@@ -10117,10 +10137,10 @@
         <v>123.62</v>
       </c>
       <c r="D199" s="5" t="n">
-        <v>105.9</v>
+        <v>106.53</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>155.79</v>
+        <v>156.72</v>
       </c>
     </row>
     <row r="200">
@@ -10136,10 +10156,10 @@
         <v>124.39</v>
       </c>
       <c r="D200" s="5" t="n">
-        <v>104.72</v>
+        <v>105.35</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>156.57</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="201">
@@ -10155,10 +10175,10 @@
         <v>75.56</v>
       </c>
       <c r="D201" s="5" t="n">
-        <v>80.68000000000001</v>
+        <v>81.17</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>94.98999999999999</v>
+        <v>95.56</v>
       </c>
     </row>
     <row r="202">
@@ -10174,10 +10194,10 @@
         <v>64.53</v>
       </c>
       <c r="D202" s="5" t="n">
-        <v>58.95</v>
+        <v>59.3</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>81.02</v>
+        <v>81.51000000000001</v>
       </c>
     </row>
     <row r="203">
@@ -10193,10 +10213,10 @@
         <v>40.07</v>
       </c>
       <c r="D203" s="5" t="n">
-        <v>42.33</v>
+        <v>42.59</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>50.64</v>
+        <v>50.94</v>
       </c>
     </row>
     <row r="204">
@@ -10212,10 +10232,10 @@
         <v>44.77</v>
       </c>
       <c r="D204" s="5" t="n">
-        <v>47.39</v>
+        <v>47.67</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>56.94</v>
+        <v>57.28</v>
       </c>
     </row>
     <row r="205">
@@ -10231,10 +10251,10 @@
         <v>64.04000000000001</v>
       </c>
       <c r="D205" s="5" t="n">
-        <v>64.36</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>81.98</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="206">
@@ -10250,10 +10270,10 @@
         <v>68.84999999999999</v>
       </c>
       <c r="D206" s="5" t="n">
-        <v>75.56</v>
+        <v>76.02</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>87.69</v>
+        <v>88.22</v>
       </c>
     </row>
     <row r="207">
@@ -10269,10 +10289,10 @@
         <v>56.61</v>
       </c>
       <c r="D207" s="5" t="n">
-        <v>57.74</v>
+        <v>58.09</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>71.73</v>
+        <v>72.16</v>
       </c>
     </row>
     <row r="208">
@@ -10288,10 +10308,10 @@
         <v>7.52</v>
       </c>
       <c r="D208" s="5" t="n">
-        <v>19.18</v>
+        <v>19.29</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>9.48</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="209">
@@ -10307,10 +10327,10 @@
         <v>40.23</v>
       </c>
       <c r="D209" s="5" t="n">
-        <v>41.44</v>
+        <v>41.69</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>50.57</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="210">
@@ -10326,10 +10346,10 @@
         <v>37.9</v>
       </c>
       <c r="D210" s="5" t="n">
-        <v>46.01</v>
+        <v>46.29</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>47.49</v>
+        <v>47.78</v>
       </c>
     </row>
     <row r="211">
@@ -10345,10 +10365,10 @@
         <v>10.26</v>
       </c>
       <c r="D211" s="5" t="n">
-        <v>20.96</v>
+        <v>21.09</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>12.82</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="212">
@@ -10364,10 +10384,10 @@
         <v>12.41</v>
       </c>
       <c r="D212" s="5" t="n">
-        <v>35.79</v>
+        <v>36</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>15.48</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="213">
@@ -10383,10 +10403,10 @@
         <v>25.88</v>
       </c>
       <c r="D213" s="5" t="n">
-        <v>27.99</v>
+        <v>28.16</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>32.21</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="214">
@@ -10402,10 +10422,10 @@
         <v>82.06999999999999</v>
       </c>
       <c r="D214" s="5" t="n">
-        <v>85.43000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>101.95</v>
+        <v>102.56</v>
       </c>
     </row>
     <row r="215">
@@ -10421,10 +10441,10 @@
         <v>62.15</v>
       </c>
       <c r="D215" s="5" t="n">
-        <v>64.61</v>
+        <v>65</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>77.02</v>
+        <v>77.48</v>
       </c>
     </row>
     <row r="216">
@@ -10440,10 +10460,10 @@
         <v>111.31</v>
       </c>
       <c r="D216" s="5" t="n">
-        <v>90.23</v>
+        <v>90.77</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>137.6</v>
+        <v>138.42</v>
       </c>
     </row>
     <row r="217">
@@ -10459,10 +10479,10 @@
         <v>96.95999999999999</v>
       </c>
       <c r="D217" s="5" t="n">
-        <v>104.07</v>
+        <v>104.69</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>119.57</v>
+        <v>120.29</v>
       </c>
     </row>
     <row r="218">
@@ -10478,10 +10498,10 @@
         <v>117.5</v>
       </c>
       <c r="D218" s="5" t="n">
-        <v>112.14</v>
+        <v>112.81</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>144.49</v>
+        <v>145.36</v>
       </c>
     </row>
     <row r="219">
@@ -10497,10 +10517,10 @@
         <v>46.43</v>
       </c>
       <c r="D219" s="5" t="n">
-        <v>53.27</v>
+        <v>53.59</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>56.93</v>
+        <v>57.28</v>
       </c>
     </row>
     <row r="220">
@@ -10516,10 +10536,10 @@
         <v>18.34</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>22.95</v>
+        <v>23.09</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>22.43</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="221">
@@ -10535,10 +10555,10 @@
         <v>9.65</v>
       </c>
       <c r="D221" s="5" t="n">
-        <v>17.7</v>
+        <v>17.81</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>11.75</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="222">
@@ -10554,10 +10574,10 @@
         <v>43.67</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>45.7</v>
+        <v>45.97</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>52.95</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="223">
@@ -10573,10 +10593,10 @@
         <v>93.66</v>
       </c>
       <c r="D223" s="5" t="n">
-        <v>84.90000000000001</v>
+        <v>85.41</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>113.09</v>
+        <v>113.76</v>
       </c>
     </row>
     <row r="224">
@@ -10592,10 +10612,10 @@
         <v>120.28</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>106.62</v>
+        <v>107.26</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>144.19</v>
+        <v>145.05</v>
       </c>
     </row>
     <row r="225">
@@ -10611,10 +10631,10 @@
         <v>44.11</v>
       </c>
       <c r="D225" s="5" t="n">
-        <v>64.54000000000001</v>
+        <v>64.92</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>52.5</v>
+        <v>52.82</v>
       </c>
     </row>
     <row r="226">
@@ -10630,10 +10650,10 @@
         <v>68.09</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>79.19</v>
+        <v>79.66</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>80.47</v>
+        <v>80.95999999999999</v>
       </c>
     </row>
     <row r="227">
@@ -10649,10 +10669,10 @@
         <v>168.67</v>
       </c>
       <c r="D227" s="5" t="n">
-        <v>179</v>
+        <v>180.08</v>
       </c>
       <c r="E227" s="5" t="n">
-        <v>198.16</v>
+        <v>199.35</v>
       </c>
     </row>
     <row r="228">
@@ -10668,10 +10688,10 @@
         <v>403.15</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>364.75</v>
+        <v>366.93</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>470.85</v>
+        <v>473.68</v>
       </c>
     </row>
     <row r="229">
@@ -10687,10 +10707,10 @@
         <v>349.33</v>
       </c>
       <c r="D229" s="5" t="n">
-        <v>351.33</v>
+        <v>353.44</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>405.6</v>
+        <v>408.04</v>
       </c>
     </row>
     <row r="230">
@@ -10706,10 +10726,10 @@
         <v>489.22</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>429.86</v>
+        <v>432.44</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>564.5700000000001</v>
+        <v>567.96</v>
       </c>
     </row>
     <row r="231">
@@ -10725,10 +10745,10 @@
         <v>226.62</v>
       </c>
       <c r="D231" s="5" t="n">
-        <v>198.48</v>
+        <v>199.67</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>259.94</v>
+        <v>261.5</v>
       </c>
     </row>
     <row r="232">
@@ -10744,10 +10764,10 @@
         <v>137.68</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>168.56</v>
+        <v>169.57</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>156.97</v>
+        <v>157.92</v>
       </c>
     </row>
     <row r="233">
@@ -10763,10 +10783,10 @@
         <v>68.95</v>
       </c>
       <c r="D233" s="5" t="n">
-        <v>105.94</v>
+        <v>106.57</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>78.13</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="234">
@@ -10782,10 +10802,10 @@
         <v>55.1</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>70.40000000000001</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>62.06</v>
+        <v>62.43</v>
       </c>
     </row>
     <row r="235">
@@ -10801,10 +10821,10 @@
         <v>14.86</v>
       </c>
       <c r="D235" s="5" t="n">
-        <v>39.66</v>
+        <v>39.9</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>16.63</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="236">
@@ -10820,10 +10840,10 @@
         <v>41.16</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>63.74</v>
+        <v>64.13</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>45.87</v>
+        <v>46.14</v>
       </c>
     </row>
     <row r="237">
@@ -10839,10 +10859,10 @@
         <v>130.19</v>
       </c>
       <c r="D237" s="5" t="n">
-        <v>107.67</v>
+        <v>108.31</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>144.43</v>
+        <v>145.3</v>
       </c>
     </row>
     <row r="238">
@@ -10858,10 +10878,10 @@
         <v>54.46</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>71.7</v>
+        <v>72.13</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>60.15</v>
+        <v>60.51</v>
       </c>
     </row>
     <row r="239">
@@ -10877,10 +10897,10 @@
         <v>81.17</v>
       </c>
       <c r="D239" s="5" t="n">
-        <v>93.63</v>
+        <v>94.2</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>89.39</v>
+        <v>89.93000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -10896,10 +10916,10 @@
         <v>236.79</v>
       </c>
       <c r="D240" s="5" t="n">
-        <v>217.76</v>
+        <v>219.07</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>260.04</v>
+        <v>261.6</v>
       </c>
     </row>
     <row r="241">
@@ -10915,10 +10935,10 @@
         <v>125.95</v>
       </c>
       <c r="D241" s="5" t="n">
-        <v>93.73</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>137.93</v>
+        <v>138.75</v>
       </c>
     </row>
     <row r="242">
@@ -10934,10 +10954,10 @@
         <v>94.95999999999999</v>
       </c>
       <c r="D242" s="5" t="n">
-        <v>79.37</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>103.59</v>
+        <v>104.21</v>
       </c>
     </row>
     <row r="243">
@@ -10953,10 +10973,10 @@
         <v>216.23</v>
       </c>
       <c r="D243" s="5" t="n">
-        <v>174.16</v>
+        <v>175.2</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>234.98</v>
+        <v>236.39</v>
       </c>
     </row>
     <row r="244">
@@ -10972,10 +10992,10 @@
         <v>34.35</v>
       </c>
       <c r="D244" s="5" t="n">
-        <v>44.73</v>
+        <v>45</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>37.19</v>
+        <v>37.41</v>
       </c>
     </row>
     <row r="245">
@@ -10991,10 +11011,10 @@
         <v>9.57</v>
       </c>
       <c r="D245" s="5" t="n">
-        <v>16.33</v>
+        <v>16.43</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>10.34</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="246">
@@ -11010,10 +11030,10 @@
         <v>48.53</v>
       </c>
       <c r="D246" s="5" t="n">
-        <v>48.43</v>
+        <v>48.72</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>52.32</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="247">
@@ -11029,10 +11049,10 @@
         <v>45.54</v>
       </c>
       <c r="D247" s="5" t="n">
-        <v>40.91</v>
+        <v>41.16</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>48.99</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="248">
@@ -11048,10 +11068,10 @@
         <v>23.49</v>
       </c>
       <c r="D248" s="5" t="n">
-        <v>35.11</v>
+        <v>35.32</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>25.19</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="249">
@@ -11067,10 +11087,10 @@
         <v>74.73999999999999</v>
       </c>
       <c r="D249" s="5" t="n">
-        <v>70.64</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>79.91</v>
+        <v>80.39</v>
       </c>
     </row>
     <row r="250">
@@ -11086,10 +11106,10 @@
         <v>70.23999999999999</v>
       </c>
       <c r="D250" s="5" t="n">
-        <v>71.56</v>
+        <v>71.98</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>74.87</v>
+        <v>75.31999999999999</v>
       </c>
     </row>
     <row r="251">
@@ -11105,10 +11125,10 @@
         <v>81.98999999999999</v>
       </c>
       <c r="D251" s="5" t="n">
-        <v>98.25</v>
+        <v>98.84</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>87.09</v>
+        <v>87.61</v>
       </c>
     </row>
     <row r="252">
@@ -11124,10 +11144,10 @@
         <v>143.45</v>
       </c>
       <c r="D252" s="5" t="n">
-        <v>143.65</v>
+        <v>144.51</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>151.85</v>
+        <v>152.76</v>
       </c>
     </row>
     <row r="253">
@@ -11143,10 +11163,10 @@
         <v>212.87</v>
       </c>
       <c r="D253" s="5" t="n">
-        <v>186.37</v>
+        <v>187.49</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>224.55</v>
+        <v>225.9</v>
       </c>
     </row>
     <row r="254">
@@ -11162,10 +11182,10 @@
         <v>295.38</v>
       </c>
       <c r="D254" s="5" t="n">
-        <v>254.27</v>
+        <v>255.8</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>311.36</v>
+        <v>313.23</v>
       </c>
     </row>
     <row r="255">
@@ -11181,10 +11201,10 @@
         <v>219.7</v>
       </c>
       <c r="D255" s="5" t="n">
-        <v>157.5</v>
+        <v>158.44</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>231.42</v>
+        <v>232.81</v>
       </c>
     </row>
     <row r="256">
@@ -11200,10 +11220,10 @@
         <v>144.76</v>
       </c>
       <c r="D256" s="5" t="n">
-        <v>84.51000000000001</v>
+        <v>85.02</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>152.37</v>
+        <v>153.28</v>
       </c>
     </row>
     <row r="257">
@@ -11219,10 +11239,10 @@
         <v>29.04</v>
       </c>
       <c r="D257" s="5" t="n">
-        <v>37.07</v>
+        <v>37.29</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>30.55</v>
+        <v>30.73</v>
       </c>
     </row>
     <row r="258">
@@ -11238,10 +11258,10 @@
         <v>49.02</v>
       </c>
       <c r="D258" s="5" t="n">
-        <v>64.03</v>
+        <v>64.41</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>51.53</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="259">
@@ -11257,10 +11277,10 @@
         <v>47.42</v>
       </c>
       <c r="D259" s="5" t="n">
-        <v>64.56999999999999</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>49.82</v>
+        <v>50.11</v>
       </c>
     </row>
     <row r="260">
@@ -11276,10 +11296,10 @@
         <v>8.76</v>
       </c>
       <c r="D260" s="5" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>9.17</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="261">
@@ -11295,10 +11315,10 @@
         <v>87.75</v>
       </c>
       <c r="D261" s="5" t="n">
-        <v>95.37</v>
+        <v>95.94</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>91.62</v>
+        <v>92.17</v>
       </c>
     </row>
     <row r="262">
@@ -11314,10 +11334,10 @@
         <v>55.45</v>
       </c>
       <c r="D262" s="5" t="n">
-        <v>64.31999999999999</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>57.72</v>
+        <v>58.07</v>
       </c>
     </row>
     <row r="263">
@@ -11333,10 +11353,10 @@
         <v>82.23</v>
       </c>
       <c r="D263" s="5" t="n">
-        <v>92.23</v>
+        <v>92.78</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>85.38</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="264">
@@ -11352,10 +11372,10 @@
         <v>93.44</v>
       </c>
       <c r="D264" s="5" t="n">
-        <v>86.29000000000001</v>
+        <v>86.81</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>96.78</v>
+        <v>97.36</v>
       </c>
     </row>
     <row r="265">
@@ -11371,10 +11391,10 @@
         <v>424.64</v>
       </c>
       <c r="D265" s="5" t="n">
-        <v>258.72</v>
+        <v>260.27</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>438.75</v>
+        <v>441.38</v>
       </c>
     </row>
     <row r="266">
@@ -11390,10 +11410,10 @@
         <v>223.67</v>
       </c>
       <c r="D266" s="5" t="n">
-        <v>169.68</v>
+        <v>170.7</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>230.09</v>
+        <v>231.47</v>
       </c>
     </row>
     <row r="267">
@@ -11409,10 +11429,10 @@
         <v>84.67</v>
       </c>
       <c r="D267" s="5" t="n">
-        <v>88.95999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>86.72</v>
+        <v>87.23999999999999</v>
       </c>
     </row>
     <row r="268">
@@ -11428,10 +11448,10 @@
         <v>57.7</v>
       </c>
       <c r="D268" s="5" t="n">
-        <v>58.74</v>
+        <v>59.09</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>58.84</v>
+        <v>59.19</v>
       </c>
     </row>
     <row r="269">
@@ -11447,10 +11467,10 @@
         <v>40.14</v>
       </c>
       <c r="D269" s="5" t="n">
-        <v>51.06</v>
+        <v>51.37</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>40.85</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="270">
@@ -11466,10 +11486,10 @@
         <v>9.94</v>
       </c>
       <c r="D270" s="5" t="n">
-        <v>32.99</v>
+        <v>33.19</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>10.1</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="271">
@@ -11485,7 +11505,7 @@
         <v>-0.41</v>
       </c>
       <c r="D271" s="5" t="n">
-        <v>28.3</v>
+        <v>28.47</v>
       </c>
       <c r="E271" s="5" t="n">
         <v>-0.42</v>
@@ -11504,10 +11524,10 @@
         <v>250.71</v>
       </c>
       <c r="D272" s="5" t="n">
-        <v>153.64</v>
+        <v>154.56</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>253</v>
+        <v>254.52</v>
       </c>
     </row>
     <row r="273">
@@ -11523,10 +11543,10 @@
         <v>34.52</v>
       </c>
       <c r="D273" s="5" t="n">
-        <v>56.25</v>
+        <v>56.59</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>34.68</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="274">
@@ -11542,10 +11562,10 @@
         <v>35.84</v>
       </c>
       <c r="D274" s="5" t="n">
-        <v>43.95</v>
+        <v>44.21</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>35.84</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="275">
@@ -11561,10 +11581,10 @@
         <v>58.97</v>
       </c>
       <c r="D275" s="5" t="n">
-        <v>54.93</v>
+        <v>55.15</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>58.97</v>
+        <v>59.21</v>
       </c>
     </row>
     <row r="276">
@@ -11580,10 +11600,10 @@
         <v>59.52</v>
       </c>
       <c r="D276" s="5" t="n">
-        <v>55.79</v>
+        <v>55.9</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>59.52</v>
+        <v>59.64</v>
       </c>
     </row>
     <row r="277">
@@ -11624,8 +11644,27 @@
         <v>108.02</v>
       </c>
     </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+      <c r="B279" s="5" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="D279" s="5" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>91.84999999999999</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B278">
+  <conditionalFormatting sqref="B2:B279">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -11637,7 +11676,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C278">
+  <conditionalFormatting sqref="C2:C279">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -11649,7 +11688,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D278">
+  <conditionalFormatting sqref="D2:D279">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -11661,7 +11700,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E278">
+  <conditionalFormatting sqref="E2:E279">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
